--- a/utair_tops_for_client_prices.xlsx
+++ b/utair_tops_for_client_prices.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -484,70 +484,63 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>UTAIR EXP — топы с поправкой на рынок (порталы vs брокер)</t>
+          <t>UTAIR EXP — топы с поправкой на рынок + фильтры выборки</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ПРАВИЛО ЦЕН:</t>
+          <t>ФИЛЬТРЫ ВЫБОРКИ:</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PROPONENT и WENCOR = порталы производителей, приоритетный источник цены</t>
+          <t>1) DDP Total (после поправки портал/BOS) &gt;= $10,000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BOS = брокер, может давать неадекватные цены. Если по P/N есть портал — строки BOS НЕ входят в DDP/Purchase/наценку</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Если портала нет: берём дистрибьюторов (AVIALL/SATAIR/…); если только BOS — оставляем с меткой BOS_ONLY</t>
+          <t>2) Исключён P/N 90010705-1 (не расходный компонент)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ПРАВИЛО ЦЕН: PROPONENT/WENCOR приоритет; BOS отбрасывается при наличии портала; иначе DISTRIBUTOR → OTHER → BOS_ONLY</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Спрос (Requests, Qty): считаются ВСЕ строки с ценой, включая BOS — это частота запросов клиента</t>
+          <t>Спрос (Requests/Qty): все строки с ценой, включая BOS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Заказы: ТАЗ / EXPENDABLE / столбец Q=2026 / точный P/N; Invoicer=М пока не фильтруем</t>
+          <t>Заказы: ТАЗ / EXPENDABLE / Q=2026 / точный P/N</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Пример: BACN11AL1 — WENCOR $370 DDP; BOS $834,000 отброшен как неадекватный</t>
+          <t>В выборке после фильтров: 306 P/N</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Сумма DDP BOS, исключённая из-за наличия портала: $1,051,900</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Priority: 96 запросов, $2,508,733 DDP (corrected), реперов: 4</t>
+          <t>Priority: 85 запросов, $2,629,997 DDP, реперов: 2</t>
         </is>
       </c>
     </row>
@@ -1044,34 +1037,34 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>810483-2</t>
+          <t>1C7003-3ABE</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>SEAL - CAP</t>
+          <t>CUSHION</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1320</v>
+        <v>8704</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2010</v>
+        <v>12400</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>63863.75</v>
+        <v>63124</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>87160</v>
+        <v>89900</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>52.3</v>
+        <v>42.5</v>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
@@ -1099,14 +1092,14 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>часто спрашивают; заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R7" s="4" t="n">
-        <v>87160</v>
+        <v>89900</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1115,43 +1108,43 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2614478</t>
+          <t>810483-2</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>SCREW, MACHINE</t>
+          <t>SEAL - CAP</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>288</v>
+        <v>18</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>106</v>
+        <v>1320</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>190</v>
+        <v>2010</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>29256</v>
+        <v>63863.75</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>54617</v>
+        <v>87160</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>52.3</v>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M8" s="3" t="n">
@@ -1170,14 +1163,14 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>часто спрашивают; заметная сумма; заказа не было — зона роста; наценка высокая</t>
+          <t>часто спрашивают; заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R8" s="4" t="n">
-        <v>59657</v>
+        <v>87160</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1186,43 +1179,43 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>90G97</t>
+          <t>67839</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>SWITCH</t>
+          <t>CARTRIDGE VALVE ASSY</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9700</v>
+        <v>3058.78</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>14800</v>
+        <v>4800</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>34700</v>
+        <v>55070.24</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>52400</v>
+        <v>81610</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>56.9</v>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="M9" s="3" t="n">
@@ -1241,14 +1234,14 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="R9" s="4" t="n">
-        <v>65200</v>
+        <v>81610</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1257,34 +1250,34 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>038845-1</t>
+          <t>310A2042-3</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>BRACKET-MOUNTING</t>
+          <t>PIN</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>735.265</v>
+        <v>5306.25</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1215</v>
+        <v>7700</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>27492.72</v>
+        <v>49237.5</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>45700</v>
+        <v>68250</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>68</v>
+        <v>43.1</v>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
@@ -1293,7 +1286,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="M10" s="3" t="n">
@@ -1316,7 +1309,7 @@
         </is>
       </c>
       <c r="R10" s="4" t="n">
-        <v>45700</v>
+        <v>68250</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>0</v>
@@ -1328,43 +1321,43 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>778000</t>
+          <t>2614478</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FILTER</t>
+          <t>SCREW, MACHINE</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>96</v>
+        <v>288</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>189.95</v>
+        <v>106</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>320</v>
+        <v>190</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>12087.45</v>
+        <v>29256</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>20670</v>
+        <v>54617</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>79.2</v>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>PROPONENT, WENCOR</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="M11" s="3" t="n">
@@ -1383,14 +1376,14 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>часто спрашивают; заметная сумма; заказа не было — зона роста; наценка высокая</t>
         </is>
       </c>
       <c r="R11" s="4" t="n">
-        <v>21410</v>
+        <v>59657</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1399,43 +1392,43 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>65C33095-5</t>
+          <t>90G97</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>GASKET</t>
+          <t>SWITCH</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>173.975</v>
+        <v>9700</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>295</v>
+        <v>14800</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>8598</v>
+        <v>34700</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>14640</v>
+        <v>52400</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>52.6</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="M12" s="3" t="n">
@@ -1454,14 +1447,14 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R12" s="4" t="n">
-        <v>54640</v>
+        <v>65200</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1470,34 +1463,34 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>65-90305-24</t>
+          <t>038845-1</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>FILTER MAINTENANCE KIT</t>
+          <t>BRACKET-MOUNTING</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>350</v>
+        <v>735.265</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>570</v>
+        <v>1215</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7639.5</v>
+        <v>27492.72</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>12610</v>
+        <v>45700</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>62.9</v>
+        <v>68</v>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
@@ -1506,7 +1499,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
       <c r="M13" s="3" t="n">
@@ -1525,14 +1518,14 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="R13" s="4" t="n">
-        <v>13180</v>
+        <v>45700</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1541,34 +1534,34 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>BACN10JR3CFD</t>
+          <t>778000</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>NUTPLATE</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>3122</v>
+        <v>96</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.3</v>
+        <v>189.95</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.3</v>
+        <v>320</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>7280</v>
+        <v>12087.45</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>10380</v>
+        <v>20670</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>87</v>
+        <v>68.8</v>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
@@ -1577,7 +1570,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>PROPONENT, WENCOR</t>
         </is>
       </c>
       <c r="M14" s="3" t="n">
@@ -1596,11 +1589,11 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="R14" s="4" t="n">
-        <v>10380</v>
+        <v>21410</v>
       </c>
       <c r="S14" s="3" t="n">
         <v>0</v>
@@ -1612,43 +1605,43 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>7577741</t>
+          <t>141A6076-1</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FILTER</t>
+          <t>PIN</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>23.125</v>
+        <v>1265</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>49</v>
+        <v>1930</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>5656.25</v>
+        <v>12190.24</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>10310</v>
+        <v>19560</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>104</v>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>54.3</v>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M15" s="3" t="n">
@@ -1667,14 +1660,14 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>повторяющийся спрос; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R15" s="4" t="n">
-        <v>10310</v>
+        <v>19560</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1683,43 +1676,43 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>649-411-959-0</t>
+          <t>65C33095-5</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>CLAMP</t>
+          <t>GASKET</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>71</v>
+        <v>173.975</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>136</v>
+        <v>295</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>996</v>
+        <v>8598</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1872</v>
+        <v>14640</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>69.7</v>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>ENGINE, SATAIR</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="M16" s="3" t="n">
@@ -1738,11 +1731,11 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>часто спрашивают; заказа не было — зона роста; наценка высокая</t>
+          <t>повторяющийся спрос; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="R16" s="4" t="n">
-        <v>5972</v>
+        <v>54640</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>2</v>
@@ -1754,43 +1747,43 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>2609573</t>
+          <t>65-90305-24</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>SHIELD, HEAT</t>
+          <t>FILTER MAINTENANCE KIT</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>840</v>
+        <v>570</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>500</v>
+        <v>7639.5</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>840</v>
+        <v>12610</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>62.9</v>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
@@ -1809,14 +1802,14 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>часто спрашивают; заказа не было — зона роста</t>
+          <t>повторяющийся спрос; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="R17" s="4" t="n">
-        <v>6138</v>
+        <v>13180</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1825,43 +1818,43 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>27325-13</t>
+          <t>BACN10JR3CFD</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>CABLE ASSY</t>
+          <t>NUTPLATE</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2</v>
+        <v>3122</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>106000</v>
+        <v>2.3</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>148000</v>
+        <v>4.3</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>212000</v>
+        <v>7280</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>296000</v>
+        <v>10380</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>87</v>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="M18" s="3" t="n">
@@ -1880,11 +1873,11 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>крупная сумма; заказа не было — зона роста; наценка уже ниже</t>
+          <t>повторяющийся спрос; большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
         </is>
       </c>
       <c r="R18" s="4" t="n">
-        <v>296000</v>
+        <v>10380</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>0</v>
@@ -1896,43 +1889,43 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>90010705-1</t>
+          <t>7577741</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>BRAKE STACK REPLACEMENT</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>3</v>
+        <v>224</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>62000</v>
+        <v>23.125</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>85900</v>
+        <v>49</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>176000</v>
+        <v>5656.25</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>245600</v>
+        <v>10310</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>104</v>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="M19" s="3" t="n">
@@ -1951,14 +1944,14 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>крупная сумма; заказа не было — зона роста; наценка уже ниже; только BOS — осторожно</t>
+          <t>повторяющийся спрос; заказа не было — зона роста; наценка высокая; цена с портала</t>
         </is>
       </c>
       <c r="R19" s="4" t="n">
-        <v>245600</v>
+        <v>10310</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1967,43 +1960,43 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>69-36694-14</t>
+          <t>27325-13</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>HOLDER ASSY</t>
+          <t>CABLE ASSY</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>165000</v>
+        <v>106000</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>210000</v>
+        <v>148000</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>165000</v>
+        <v>212000</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>210000</v>
+        <v>296000</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>39.6</v>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="M20" s="3" t="n">
@@ -2022,14 +2015,14 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>крупная сумма; заказа не было — зона роста; наценка уже ниже; только BOS — осторожно</t>
+          <t>крупная сумма; заказа не было — зона роста; наценка уже ниже</t>
         </is>
       </c>
       <c r="R20" s="4" t="n">
-        <v>210000</v>
+        <v>296000</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2038,34 +2031,34 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>SG8191-1</t>
+          <t>69-36694-14</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>PHOTOLUMINESCENT STRIP</t>
+          <t>HOLDER ASSY</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1968.29</v>
+        <v>165000</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3000</v>
+        <v>210000</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>92509.63</v>
+        <v>165000</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>141000</v>
+        <v>210000</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>52.4</v>
+        <v>27.3</v>
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
@@ -2093,14 +2086,14 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>крупная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>крупная сумма; заказа не было — зона роста; наценка уже ниже; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R21" s="4" t="n">
-        <v>141000</v>
+        <v>210000</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2109,34 +2102,34 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>65C80736-185</t>
+          <t>SG8191-1</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>KIT TRACK</t>
+          <t>PHOTOLUMINESCENT STRIP</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1</v>
+        <v>154</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>86000</v>
+        <v>1968.29</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>122000</v>
+        <v>3000</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>86000</v>
+        <v>92509.63</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>122000</v>
+        <v>141000</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>41.9</v>
+        <v>52.4</v>
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
@@ -2168,10 +2161,10 @@
         </is>
       </c>
       <c r="R22" s="4" t="n">
-        <v>122000</v>
+        <v>141000</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -2180,69 +2173,69 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>11-10865</t>
+          <t>65C80736-185</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>AIR FILTER</t>
+          <t>KIT TRACK</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>570</v>
+        <v>86000</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>960</v>
+        <v>122000</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2900</v>
+        <v>86000</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4760</v>
+        <v>122000</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>41.9</v>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>AVIALL, SATAIR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>крупная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>122000</v>
+      </c>
+      <c r="S23" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" s="4" t="n">
-        <v>680</v>
-      </c>
-      <c r="P23" s="9" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>часто спрашивают; уже покупали у нас — репер</t>
-        </is>
-      </c>
-      <c r="R23" s="4" t="n">
-        <v>6220</v>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -2251,69 +2244,69 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>R287P06</t>
+          <t>3885057-2</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>NIPPLE</t>
+          <t>DUCT</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>135</v>
+        <v>74167.5</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>220</v>
+        <v>108000</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5710</v>
+        <v>74167.5</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>9340</v>
+        <v>108000</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>45.6</v>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>ENGINE, SATAIR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>крупная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+        </is>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>108000</v>
+      </c>
+      <c r="S24" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="O24" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="P24" s="9" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t>повторяющийся спрос; уже покупали у нас — репер</t>
-        </is>
-      </c>
-      <c r="R24" s="4" t="n">
-        <v>9340</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2322,53 +2315,53 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>332A2341-4</t>
+          <t>649-411-983-0</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>LINK ASSY</t>
+          <t>CLAMP</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1200</v>
+        <v>429</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1830</v>
+        <v>660</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3480</v>
+        <v>8580</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5610</v>
+        <v>13200</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>53.8</v>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>ENGINE</t>
         </is>
       </c>
       <c r="M25" s="3" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2400</v>
+        <v>1080</v>
       </c>
       <c r="P25" s="9" t="inlineStr">
         <is>
@@ -2377,11 +2370,11 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; уже покупали у нас — репер; цена с портала</t>
+          <t>повторяющийся спрос; уже покупали у нас — репер</t>
         </is>
       </c>
       <c r="R25" s="4" t="n">
-        <v>10900</v>
+        <v>14220</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>1</v>
@@ -2393,53 +2386,53 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>J522P53</t>
+          <t>ATF14</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>REDUCER</t>
+          <t>BEARING</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>81</v>
+        <v>920</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>165</v>
+        <v>1500</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>810</v>
+        <v>6440</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1734</v>
+        <v>10500</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>103.7</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>63</v>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>840</v>
+        <v>3200</v>
       </c>
       <c r="P26" s="9" t="inlineStr">
         <is>
@@ -2448,14 +2441,14 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; уже покупали у нас — репер; наценка высокая</t>
+          <t>уже покупали у нас — репер; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R26" s="4" t="n">
-        <v>2924</v>
+        <v>10500</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2739,69 +2732,69 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>11-10865</t>
+          <t>31460-5</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>AIR FILTER</t>
+          <t>HYDRAULIC TIMER</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>570</v>
+        <v>6050.54</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>960</v>
+        <v>8400</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>2900</v>
+        <v>414727</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>4760</v>
+        <v>566800</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>38.8</v>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>AVIALL, SATAIR</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>680</v>
-      </c>
-      <c r="P4" s="9" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>0</v>
+      </c>
+      <c r="P4" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>часто спрашивают; уже покупали у нас — репер</t>
+          <t>часто спрашивают; крупная сумма; заказа не было — зона роста; наценка уже ниже; цена с портала</t>
         </is>
       </c>
       <c r="R4" s="4" t="n">
-        <v>6220</v>
+        <v>566800</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2810,43 +2803,43 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>31460-5</t>
+          <t>810483-2</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>HYDRAULIC TIMER</t>
+          <t>SEAL - CAP</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>6050.54</v>
+        <v>1320</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>8400</v>
+        <v>2010</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>414727</v>
+        <v>63863.75</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>566800</v>
+        <v>87160</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>52.3</v>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M5" s="3" t="n">
@@ -2865,14 +2858,14 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>часто спрашивают; крупная сумма; заказа не было — зона роста; наценка уже ниже; цена с портала</t>
+          <t>часто спрашивают; заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R5" s="4" t="n">
-        <v>566800</v>
+        <v>87160</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2881,43 +2874,43 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>810483-2</t>
+          <t>90G97</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>SEAL - CAP</t>
+          <t>SWITCH</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1320</v>
+        <v>9700</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2010</v>
+        <v>14800</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>63863.75</v>
+        <v>34700</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>87160</v>
+        <v>52400</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>52.6</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="M6" s="3" t="n">
@@ -2936,14 +2929,14 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>часто спрашивают; заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R6" s="4" t="n">
-        <v>87160</v>
+        <v>65200</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2952,43 +2945,43 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>649-411-959-0</t>
+          <t>038845-1</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>CLAMP</t>
+          <t>BRACKET-MOUNTING</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>71</v>
+        <v>735.265</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>136</v>
+        <v>1215</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>996</v>
+        <v>27492.72</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1872</v>
+        <v>45700</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>68</v>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>ENGINE, SATAIR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
       <c r="M7" s="3" t="n">
@@ -3007,14 +3000,14 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>часто спрашивают; заказа не было — зона роста; наценка высокая</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="R7" s="4" t="n">
-        <v>5972</v>
+        <v>45700</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3023,43 +3016,43 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2609573</t>
+          <t>778000</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>SHIELD, HEAT</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>500</v>
+        <v>189.95</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>840</v>
+        <v>320</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>500</v>
+        <v>12087.45</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>840</v>
+        <v>20670</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>68.8</v>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>PROPONENT, WENCOR</t>
         </is>
       </c>
       <c r="M8" s="3" t="n">
@@ -3078,14 +3071,14 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>часто спрашивают; заказа не было — зона роста</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="R8" s="4" t="n">
-        <v>6138</v>
+        <v>21410</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3094,43 +3087,43 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>90G97</t>
+          <t>141A6076-1</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>SWITCH</t>
+          <t>PIN</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9700</v>
+        <v>1265</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>14800</v>
+        <v>1930</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>34700</v>
+        <v>12190.24</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>52400</v>
+        <v>19560</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>54.3</v>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M9" s="3" t="n">
@@ -3149,14 +3142,14 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста</t>
+          <t>повторяющийся спрос; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R9" s="4" t="n">
-        <v>65200</v>
+        <v>19560</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -3165,34 +3158,34 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>038845-1</t>
+          <t>65C33095-5</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>BRACKET-MOUNTING</t>
+          <t>GASKET</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>735.265</v>
+        <v>173.975</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1215</v>
+        <v>295</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>27492.72</v>
+        <v>8598</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>45700</v>
+        <v>14640</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>68</v>
+        <v>69.7</v>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
@@ -3201,7 +3194,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="M10" s="3" t="n">
@@ -3220,14 +3213,14 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="R10" s="4" t="n">
-        <v>45700</v>
+        <v>54640</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -3236,34 +3229,34 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>778000</t>
+          <t>65-90305-24</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FILTER</t>
+          <t>FILTER MAINTENANCE KIT</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>189.95</v>
+        <v>350</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>320</v>
+        <v>570</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>12087.45</v>
+        <v>7639.5</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>20670</v>
+        <v>12610</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>68.8</v>
+        <v>62.9</v>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
@@ -3272,7 +3265,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>PROPONENT, WENCOR</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="M11" s="3" t="n">
@@ -3291,14 +3284,14 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="R11" s="4" t="n">
-        <v>21410</v>
+        <v>13180</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -3307,31 +3300,31 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>141A6076-1</t>
+          <t>9247</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>PIN</t>
+          <t>SCREW</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1265</v>
+        <v>1848</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1930</v>
+        <v>2850</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>12190.24</v>
+        <v>7194</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>19560</v>
+        <v>11108</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>54.3</v>
@@ -3366,7 +3359,7 @@
         </is>
       </c>
       <c r="R12" s="4" t="n">
-        <v>19560</v>
+        <v>11108</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>4</v>
@@ -3378,34 +3371,34 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>65C33095-5</t>
+          <t>7577741</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>GASKET</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>105</v>
+        <v>224</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>173.975</v>
+        <v>23.125</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>295</v>
+        <v>49</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>8598</v>
+        <v>5656.25</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>14640</v>
+        <v>10310</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>69.7</v>
+        <v>104</v>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
@@ -3433,14 +3426,14 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос; заказа не было — зона роста; наценка высокая; цена с портала</t>
         </is>
       </c>
       <c r="R13" s="4" t="n">
-        <v>54640</v>
+        <v>10310</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3449,43 +3442,43 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>65-90305-24</t>
+          <t>RAA2196-4</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>FILTER MAINTENANCE KIT</t>
+          <t>SWITCH</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>350</v>
+        <v>20300</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>570</v>
+        <v>28000</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>7639.5</v>
+        <v>121800</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>12610</v>
+        <v>164800</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>37.9</v>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="M14" s="3" t="n">
@@ -3504,14 +3497,14 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос; крупная сумма; заказа не было — зона роста; наценка уже ниже</t>
         </is>
       </c>
       <c r="R14" s="4" t="n">
-        <v>13180</v>
+        <v>164800</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3520,43 +3513,43 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>810-2042/K</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>SCREW</t>
+          <t>ULB 90?DAY BATTERY REPLACEMENT KIT</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1848</v>
+        <v>2000</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2850</v>
+        <v>2790</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>7194</v>
+        <v>112000</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>11108</v>
+        <v>156240</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="K15" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>40.2</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="M15" s="3" t="n">
@@ -3575,14 +3568,14 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос; крупная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R15" s="4" t="n">
-        <v>11108</v>
+        <v>251440</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3591,43 +3584,43 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>7577741</t>
+          <t>CR3524-6-03</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>FILTER</t>
+          <t>RIVET</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>224</v>
+        <v>1360</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>23.125</v>
+        <v>64.5</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>5656.25</v>
+        <v>87400</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>10310</v>
+        <v>133900</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>104</v>
-      </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>61.4</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="M16" s="3" t="n">
@@ -3646,14 +3639,14 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>повторяющийся спрос; крупная сумма; большой объём шт; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R16" s="4" t="n">
-        <v>10310</v>
+        <v>136300</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -3662,69 +3655,69 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>R287P06</t>
+          <t>1C7003-3ABE</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>NIPPLE</t>
+          <t>CUSHION</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>135</v>
+        <v>8704</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>220</v>
+        <v>12400</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>5710</v>
+        <v>63124</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>9340</v>
+        <v>89900</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>42.5</v>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>ENGINE, SATAIR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="P17" s="9" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; уже покупали у нас — репер</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R17" s="4" t="n">
-        <v>9340</v>
+        <v>89900</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -3733,34 +3726,34 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>9048156</t>
+          <t>67839</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>SEAL</t>
+          <t>CARTRIDGE VALVE ASSY</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>27.655</v>
+        <v>3058.78</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>47</v>
+        <v>4800</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4415.5</v>
+        <v>55070.24</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>7420</v>
+        <v>81610</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>81.7</v>
+        <v>56.9</v>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
@@ -3788,11 +3781,11 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="R18" s="4" t="n">
-        <v>7420</v>
+        <v>81610</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>0</v>
@@ -3804,43 +3797,43 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>65-90305-85</t>
+          <t>310A2042-3</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>FILTER MAINTENANCE KIT</t>
+          <t>PIN</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>92</v>
+        <v>5306.25</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>164</v>
+        <v>7700</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>4140</v>
+        <v>49237.5</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>7420</v>
+        <v>68250</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>43.1</v>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="M19" s="3" t="n">
@@ -3859,11 +3852,11 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заказа не было — зона роста; наценка высокая</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="R19" s="4" t="n">
-        <v>7420</v>
+        <v>68250</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>0</v>
@@ -3875,43 +3868,43 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>BACC30BL8</t>
+          <t>2100002-01-104</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>COLLAR</t>
+          <t>RESTRAINT ASSY</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>690</v>
+        <v>25</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>8</v>
+        <v>4579.5</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>16.7</v>
+        <v>7005</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3920</v>
+        <v>36636</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>7400</v>
+        <v>55220</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>108.7</v>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>OTHER</t>
+        <v>53</v>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>PROPONENT</t>
         </is>
       </c>
       <c r="M20" s="3" t="n">
@@ -3930,11 +3923,11 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; большой объём шт; заказа не было — зона роста; наценка высокая</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="R20" s="4" t="n">
-        <v>13600</v>
+        <v>73220</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>1</v>
@@ -3946,43 +3939,43 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>995000-01</t>
+          <t>141A6075-3</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>TOOL-OXYGEN MANUAL RELEASE</t>
+          <t>ARM ASSY</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>400</v>
+        <v>9537.5</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>660</v>
+        <v>13800</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>4000</v>
+        <v>38637.5</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>6600</v>
+        <v>55000</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>41.8</v>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>SATAIR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M21" s="3" t="n">
@@ -4001,14 +3994,14 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заказа не было — зона роста</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R21" s="4" t="n">
-        <v>6600</v>
+        <v>55000</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -4017,43 +4010,43 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>65-90305-88</t>
+          <t>113A9309-1</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>KIT - CFM56-7 FUEL PUMP FILTER</t>
+          <t>BUSHING-PIVOT BOLT</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>170</v>
+        <v>2670</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>285</v>
+        <v>4130</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3400</v>
+        <v>30920</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>5700</v>
+        <v>48360</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>54.8</v>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="M22" s="3" t="n">
@@ -4072,14 +4065,14 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заказа не было — зона роста</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="R22" s="4" t="n">
-        <v>14350</v>
+        <v>84160</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -4088,69 +4081,69 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>332A2341-4</t>
+          <t>310A2029-11</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>LINK ASSY</t>
+          <t>BOLT-SPECIAL</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1200</v>
+        <v>1822.1</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1830</v>
+        <v>2300</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3480</v>
+        <v>32496.8</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5610</v>
+        <v>45710</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>52.4</v>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2400</v>
-      </c>
-      <c r="P23" s="9" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; уже покупали у нас — репер; цена с портала</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R23" s="4" t="n">
-        <v>10900</v>
+        <v>45710</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -4159,43 +4152,43 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>BACB30PN4-6</t>
+          <t>815523-1</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>BOLT</t>
+          <t>PACKING</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>205</v>
+        <v>31</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>11</v>
+        <v>1320</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>20</v>
+        <v>2010</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2220</v>
+        <v>30135</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4090</v>
+        <v>44810</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>52.3</v>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M24" s="3" t="n">
@@ -4214,14 +4207,14 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R24" s="4" t="n">
-        <v>4090</v>
+        <v>44810</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -4230,34 +4223,34 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>762096</t>
+          <t>1024366-311BHV</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>WASHER</t>
+          <t>BUMPER-ENDBAY</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>510</v>
+        <v>270</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>850</v>
+        <v>415</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2040</v>
+        <v>29700</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3400</v>
+        <v>39800</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>66.7</v>
+        <v>53.7</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
@@ -4266,7 +4259,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>AVIALL, SATAIR</t>
+          <t>SATAIR</t>
         </is>
       </c>
       <c r="M25" s="3" t="n">
@@ -4285,14 +4278,14 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заказа не было — зона роста</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R25" s="4" t="n">
-        <v>3400</v>
+        <v>45700</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -4301,34 +4294,34 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>2-256S317-60</t>
+          <t>2100002-01-129</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>PACKING</t>
+          <t>RESTRAINT SYSTEM - SYS</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E26" s="3" t="n">
-        <v>96</v>
-      </c>
       <c r="F26" s="4" t="n">
-        <v>12.92</v>
+        <v>5544.53</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>25</v>
+        <v>8200</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1371.76</v>
+        <v>22178.12</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2555</v>
+        <v>33000</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>82.2</v>
+        <v>47.9</v>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
@@ -4337,7 +4330,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
       <c r="M26" s="3" t="n">
@@ -4356,11 +4349,11 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="R26" s="4" t="n">
-        <v>2555</v>
+        <v>33000</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>0</v>
@@ -4372,34 +4365,34 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>411N1521-2B</t>
+          <t>332A2930-90</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>LATCH</t>
+          <t>BRACKET ASSY</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>372.155</v>
+        <v>5500</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>610</v>
+        <v>8100</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1483.67</v>
+        <v>18100</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2440</v>
+        <v>26100</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>65</v>
+        <v>43.1</v>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
@@ -4427,14 +4420,14 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R27" s="4" t="n">
-        <v>2440</v>
+        <v>26100</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -4443,34 +4436,34 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>J522P53</t>
+          <t>65-0028-11</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>REDUCER</t>
+          <t>LIGHT</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>81</v>
+        <v>2890</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>165</v>
+        <v>4550</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>810</v>
+        <v>17340</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1734</v>
+        <v>25800</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>103.7</v>
+        <v>57.4</v>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
@@ -4483,29 +4476,29 @@
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>840</v>
-      </c>
-      <c r="P28" s="9" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>0</v>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; уже покупали у нас — репер; наценка высокая</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R28" s="4" t="n">
-        <v>2924</v>
+        <v>25800</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -4514,43 +4507,43 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>1A296-0217HS</t>
+          <t>340-007-203-0</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>COVER-BACK CUSHION</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E29" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="F29" s="4" t="n">
-        <v>870</v>
+        <v>5686</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1420</v>
+        <v>8500</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>870</v>
+        <v>17058</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1420</v>
+        <v>25400</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="K29" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>49.5</v>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>ENGINE</t>
         </is>
       </c>
       <c r="M29" s="3" t="n">
@@ -4569,14 +4562,14 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R29" s="4" t="n">
-        <v>22560</v>
+        <v>27960</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -4585,43 +4578,43 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>AS3237-06</t>
+          <t>5011211</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>BOLT</t>
+          <t>PIN INDICATOR</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>8.33</v>
+        <v>490</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>16.5</v>
+        <v>800</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>648.2</v>
+        <v>12740</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1312.5</v>
+        <v>19920</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="K30" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>63.3</v>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>PROPONENT, WENCOR</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="M30" s="3" t="n">
@@ -4640,11 +4633,11 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>повторяющийся спрос; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R30" s="4" t="n">
-        <v>1312.5</v>
+        <v>19920</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>0</v>
@@ -4656,69 +4649,69 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>AS1895-7-200</t>
+          <t>0A296-0216HS</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>SEAL</t>
+          <t>COVER-SEAT</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>21.475</v>
+        <v>1040</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>43</v>
+        <v>1750</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>437.25</v>
+        <v>11430</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>840</v>
+        <v>19180</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="K31" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>68.3</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>PROPONENT, WENCOR</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="M31" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>378</v>
-      </c>
-      <c r="P31" s="9" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>0</v>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; уже покупали у нас — репер; наценка высокая; цена с портала</t>
+          <t>повторяющийся спрос; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R31" s="4" t="n">
-        <v>1635</v>
+        <v>19180</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5002,34 +4995,34 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>90010705-1</t>
+          <t>69-36694-14</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>BRAKE STACK REPLACEMENT</t>
+          <t>HOLDER ASSY</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>62000</v>
+        <v>165000</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>85900</v>
+        <v>210000</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>176000</v>
+        <v>165000</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>245600</v>
+        <v>210000</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>39</v>
+        <v>27.3</v>
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
@@ -5061,10 +5054,10 @@
         </is>
       </c>
       <c r="R4" s="4" t="n">
-        <v>245600</v>
+        <v>210000</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -5073,43 +5066,43 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>69-36694-14</t>
+          <t>RAA2196-4</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>HOLDER ASSY</t>
+          <t>SWITCH</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>165000</v>
+        <v>20300</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>210000</v>
+        <v>28000</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>165000</v>
+        <v>121800</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>210000</v>
+        <v>164800</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>37.9</v>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="M5" s="3" t="n">
@@ -5128,14 +5121,14 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>крупная сумма; заказа не было — зона роста; наценка уже ниже; только BOS — осторожно</t>
+          <t>повторяющийся спрос; крупная сумма; заказа не было — зона роста; наценка уже ниже</t>
         </is>
       </c>
       <c r="R5" s="4" t="n">
-        <v>210000</v>
+        <v>164800</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5144,43 +5137,43 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>RAA2196-4</t>
+          <t>810-2042/K</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>SWITCH</t>
+          <t>ULB 90?DAY BATTERY REPLACEMENT KIT</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>20300</v>
+        <v>2000</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>28000</v>
+        <v>2790</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>121800</v>
+        <v>112000</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>164800</v>
+        <v>156240</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>37.9</v>
+        <v>40.2</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>DISTRIBUTOR</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="M6" s="3" t="n">
@@ -5199,14 +5192,14 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; крупная сумма; заказа не было — зона роста; наценка уже ниже</t>
+          <t>повторяющийся спрос; крупная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R6" s="4" t="n">
-        <v>164800</v>
+        <v>251440</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -5215,43 +5208,43 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>810-2042/K</t>
+          <t>SG8191-1</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>ULB 90?DAY BATTERY REPLACEMENT KIT</t>
+          <t>PHOTOLUMINESCENT STRIP</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2000</v>
+        <v>1968.29</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2790</v>
+        <v>3000</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>112000</v>
+        <v>92509.63</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>156240</v>
+        <v>141000</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>OTHER</t>
+        <v>52.4</v>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M7" s="3" t="n">
@@ -5270,14 +5263,14 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; крупная сумма; заказа не было — зона роста</t>
+          <t>крупная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R7" s="4" t="n">
-        <v>251440</v>
+        <v>141000</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -5286,43 +5279,43 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>SG8191-1</t>
+          <t>3036376</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>PHOTOLUMINESCENT STRIP</t>
+          <t>FILTER ELEMENT</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1968.29</v>
+        <v>1710</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3000</v>
+        <v>2505</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>92509.63</v>
+        <v>94510</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>141000</v>
+        <v>139750</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>52.9</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>AVIALL, SATAIR</t>
         </is>
       </c>
       <c r="M8" s="3" t="n">
@@ -5341,14 +5334,14 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>крупная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>часто спрашивают; крупная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R8" s="4" t="n">
-        <v>141000</v>
+        <v>147740</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5357,43 +5350,43 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>3036376</t>
+          <t>CR3524-6-03</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FILTER ELEMENT</t>
+          <t>RIVET</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>116</v>
+        <v>1360</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1710</v>
+        <v>64.5</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2505</v>
+        <v>104</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>94510</v>
+        <v>87400</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>139750</v>
+        <v>133900</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>52.9</v>
+        <v>61.4</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>DISTRIBUTOR</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>AVIALL, SATAIR</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="M9" s="3" t="n">
@@ -5412,14 +5405,14 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>часто спрашивают; крупная сумма; заказа не было — зона роста</t>
+          <t>повторяющийся спрос; крупная сумма; большой объём шт; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R9" s="4" t="n">
-        <v>147740</v>
+        <v>136300</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -5428,43 +5421,43 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>CR3524-6-03</t>
+          <t>65C80736-185</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>KIT TRACK</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1360</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>64.5</v>
+        <v>86000</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>104</v>
+        <v>122000</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>87400</v>
+        <v>86000</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>133900</v>
+        <v>122000</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>OTHER</t>
+        <v>41.9</v>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M10" s="3" t="n">
@@ -5483,11 +5476,11 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; крупная сумма; большой объём шт; заказа не было — зона роста</t>
+          <t>крупная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R10" s="4" t="n">
-        <v>136300</v>
+        <v>122000</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>1</v>
@@ -5499,12 +5492,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>65C80736-185</t>
+          <t>3885057-2</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>KIT TRACK</t>
+          <t>DUCT</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -5514,19 +5507,19 @@
         <v>1</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>86000</v>
+        <v>74167.5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>122000</v>
+        <v>108000</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>86000</v>
+        <v>74167.5</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>122000</v>
+        <v>108000</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>41.9</v>
+        <v>45.6</v>
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
@@ -5558,7 +5551,7 @@
         </is>
       </c>
       <c r="R11" s="4" t="n">
-        <v>122000</v>
+        <v>108000</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>1</v>
@@ -5570,34 +5563,34 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>3885057-2</t>
+          <t>65-47951Y5</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>DUCT</t>
+          <t>SCUFF PLATE</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>74167.5</v>
+        <v>12100</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>108000</v>
+        <v>17800</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>74167.5</v>
+        <v>72600</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>108000</v>
+        <v>106800</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>45.6</v>
+        <v>47.1</v>
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
@@ -5629,7 +5622,7 @@
         </is>
       </c>
       <c r="R12" s="4" t="n">
-        <v>108000</v>
+        <v>106800</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>1</v>
@@ -5641,34 +5634,34 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>65-47951Y5</t>
+          <t>314-2162-1</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>SCUFF PLATE</t>
+          <t>PANEL ASSY</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>12100</v>
+        <v>36000</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>17800</v>
+        <v>51100</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>72600</v>
+        <v>72000</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>106800</v>
+        <v>102200</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>47.1</v>
+        <v>41.9</v>
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
@@ -5700,7 +5693,7 @@
         </is>
       </c>
       <c r="R13" s="4" t="n">
-        <v>106800</v>
+        <v>102200</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>1</v>
@@ -5712,43 +5705,43 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>314-2162-1</t>
+          <t>5000-1-01A-2396</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>PANEL ASSY</t>
+          <t>RESTRAINT ASSY</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>36000</v>
+        <v>12700</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>51100</v>
+        <v>18800</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>72000</v>
+        <v>63500</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>102200</v>
+        <v>94000</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>48</v>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SATAIR</t>
         </is>
       </c>
       <c r="M14" s="3" t="n">
@@ -5767,14 +5760,14 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>крупная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R14" s="4" t="n">
-        <v>102200</v>
+        <v>94000</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5783,34 +5776,34 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>5000-1-01A-2396</t>
+          <t>2028M21P02</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>RESTRAINT ASSY</t>
+          <t>COUPLING</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>12700</v>
+        <v>22000</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>18800</v>
+        <v>31200</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>63500</v>
+        <v>66000</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>94000</v>
+        <v>93600</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>48</v>
+        <v>41.8</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
@@ -5819,7 +5812,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>SATAIR</t>
+          <t>ENGINE</t>
         </is>
       </c>
       <c r="M15" s="3" t="n">
@@ -5842,7 +5835,7 @@
         </is>
       </c>
       <c r="R15" s="4" t="n">
-        <v>94000</v>
+        <v>93600</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>0</v>
@@ -5854,69 +5847,69 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2028M21P02</t>
+          <t>1C7003-3ABE</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>COUPLING</t>
+          <t>CUSHION</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>8704</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>12400</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>63124</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>89900</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>89900</v>
+      </c>
+      <c r="S16" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>22000</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>31200</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>66000</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>93600</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>ENGINE</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>заметная сумма; заказа не было — зона роста</t>
-        </is>
-      </c>
-      <c r="R16" s="4" t="n">
-        <v>93600</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5925,34 +5918,34 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>1C7003-3ABE</t>
+          <t>CBR8260-123</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>CUSHION</t>
+          <t>KIT</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>7</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>8704</v>
+        <v>8500</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>12400</v>
+        <v>12050</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>63124</v>
+        <v>63400</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>89900</v>
+        <v>89600</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>42.5</v>
+        <v>41.9</v>
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
@@ -5980,14 +5973,14 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R17" s="4" t="n">
-        <v>89900</v>
+        <v>89600</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -5996,12 +5989,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>CBR8260-123</t>
+          <t>2606703</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>KIT</t>
+          <t>PLATE, PRESSURE</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -6011,28 +6004,28 @@
         <v>7</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>8500</v>
+        <v>12100</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>12050</v>
+        <v>17800</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>63400</v>
+        <v>60500</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>89600</v>
+        <v>89000</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="K18" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>47.1</v>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="M18" s="3" t="n">
@@ -6051,14 +6044,14 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R18" s="4" t="n">
-        <v>89600</v>
+        <v>100600</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -6067,43 +6060,43 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>2606703</t>
+          <t>FO45/CW/BCAC</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>PLATE, PRESSURE</t>
+          <t>LAMP</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>12100</v>
+        <v>1440</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>17800</v>
+        <v>2200</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>60500</v>
+        <v>57600</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>89000</v>
+        <v>88000</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>52.8</v>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M19" s="3" t="n">
@@ -6122,11 +6115,11 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>заметная сумма; заказа не было — зона роста</t>
+          <t>заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R19" s="4" t="n">
-        <v>100600</v>
+        <v>88000</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>1</v>
@@ -6138,34 +6131,34 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>FO45/CW/BCAC</t>
+          <t>69-58822-3</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>LAMP</t>
+          <t>ROD ASSY</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1440</v>
+        <v>31000</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2200</v>
+        <v>44000</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>57600</v>
+        <v>62000</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>88000</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>52.8</v>
+        <v>41.9</v>
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
@@ -6209,34 +6202,34 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>69-58822-3</t>
+          <t>65-53844-26</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>ROD ASSY</t>
+          <t>TRACK</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>31000</v>
+        <v>60197.18</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>44000</v>
+        <v>88000</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>62000</v>
+        <v>60197.18</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>88000</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>41.9</v>
+        <v>46.2</v>
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
@@ -6280,34 +6273,34 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>65-53844-26</t>
+          <t>810483-2</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>TRACK</t>
+          <t>SEAL - CAP</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>60197.18</v>
+        <v>1320</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>88000</v>
+        <v>2010</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>60197.18</v>
+        <v>63863.75</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>88000</v>
+        <v>87160</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>46.2</v>
+        <v>52.3</v>
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
@@ -6335,14 +6328,14 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>часто спрашивают; заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R22" s="4" t="n">
-        <v>88000</v>
+        <v>87160</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -6351,34 +6344,34 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>810483-2</t>
+          <t>105021</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>SEAL - CAP</t>
+          <t>FLANGED FLEXIBLE SLEEVE</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1320</v>
+        <v>63000</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2010</v>
+        <v>86000</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>63863.75</v>
+        <v>63000</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>87160</v>
+        <v>86000</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>52.3</v>
+        <v>36.5</v>
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
@@ -6406,14 +6399,14 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>часто спрашивают; заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>заметная сумма; заказа не было — зона роста; наценка уже ниже; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R23" s="4" t="n">
-        <v>87160</v>
+        <v>86000</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -6422,43 +6415,43 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>105021</t>
+          <t>7377543</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FLANGED FLEXIBLE SLEEVE</t>
+          <t>BRAKE LININGS</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>63000</v>
+        <v>180</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>86000</v>
+        <v>280</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>63000</v>
+        <v>54000</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>86000</v>
+        <v>84000</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>55.6</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="M24" s="3" t="n">
@@ -6477,14 +6470,14 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>заметная сумма; заказа не было — зона роста; наценка уже ниже; только BOS — осторожно</t>
+          <t>заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R24" s="4" t="n">
-        <v>86000</v>
+        <v>84000</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -6493,43 +6486,43 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>7377543</t>
+          <t>65-2346-5</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>BRAKE LININGS</t>
+          <t>SNUBBER ASSY</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>300</v>
+        <v>3</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>180</v>
+        <v>20300</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>280</v>
+        <v>28000</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>54000</v>
+        <v>60900</v>
       </c>
       <c r="I25" s="4" t="n">
         <v>84000</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>37.9</v>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M25" s="3" t="n">
@@ -6548,14 +6541,14 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>заметная сумма; заказа не было — зона роста</t>
+          <t>заметная сумма; заказа не было — зона роста; наценка уже ниже; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R25" s="4" t="n">
         <v>84000</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -6564,28 +6557,28 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>65-2346-5</t>
+          <t>65-47951-13</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>SNUBBER ASSY</t>
+          <t>PLATE</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>20300</v>
+        <v>60898.66</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>28000</v>
+        <v>84000</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>60900</v>
+        <v>60898.66</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>84000</v>
@@ -6635,43 +6628,43 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>65-47951-13</t>
+          <t>67839</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>PLATE</t>
+          <t>CARTRIDGE VALVE ASSY</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>60898.66</v>
+        <v>3058.78</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>84000</v>
+        <v>4800</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>60898.66</v>
+        <v>55070.24</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>84000</v>
+        <v>81610</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>56.9</v>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="M27" s="3" t="n">
@@ -6690,14 +6683,14 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>заметная сумма; заказа не было — зона роста; наценка уже ниже; только BOS — осторожно</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="R27" s="4" t="n">
-        <v>84000</v>
+        <v>81610</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -6706,43 +6699,43 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>67839</t>
+          <t>352A1547P1</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>CARTRIDGE VALVE ASSY</t>
+          <t>MOUNT</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3058.78</v>
+        <v>13200</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4800</v>
+        <v>18800</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>55070.24</v>
+        <v>52800</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>81610</v>
+        <v>75200</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="K28" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>42.4</v>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M28" s="3" t="n">
@@ -6761,14 +6754,14 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R28" s="4" t="n">
-        <v>81610</v>
+        <v>75200</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -6777,34 +6770,34 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>352A1547P1</t>
+          <t>453A2610-6</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>MOUNT</t>
+          <t>PANEL</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>13200</v>
+        <v>24324.065</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>18800</v>
+        <v>34600</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>52800</v>
+        <v>48648.13</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>75200</v>
+        <v>69200</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
@@ -6836,10 +6829,10 @@
         </is>
       </c>
       <c r="R29" s="4" t="n">
-        <v>75200</v>
+        <v>69200</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -6848,43 +6841,43 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>453A2610-6</t>
+          <t>310A2042-3</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>PANEL</t>
+          <t>PIN</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>24324.065</v>
+        <v>5306.25</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>34600</v>
+        <v>7700</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>48648.13</v>
+        <v>49237.5</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>69200</v>
+        <v>68250</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="K30" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>43.1</v>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="M30" s="3" t="n">
@@ -6903,14 +6896,14 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="R30" s="4" t="n">
-        <v>69200</v>
+        <v>68250</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -6919,43 +6912,43 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>310A2042-3</t>
+          <t>314-2162-3</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>PIN</t>
+          <t>PANEL ASSY</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5306.25</v>
+        <v>48000</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>7700</v>
+        <v>68100</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>49237.5</v>
+        <v>48000</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>68250</v>
+        <v>68100</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="K31" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>41.9</v>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M31" s="3" t="n">
@@ -6974,14 +6967,14 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R31" s="4" t="n">
-        <v>68250</v>
+        <v>68100</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7123,43 +7116,43 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>BACR15DR3AC3</t>
+          <t>BACN10JR3CFD</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>NUTPLATE</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5000</v>
+        <v>3122</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>9.1</v>
+        <v>4.3</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>215.6</v>
+        <v>7280</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>400.4</v>
+        <v>10380</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="K2" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>87</v>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="M2" s="3" t="n">
@@ -7178,14 +7171,14 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая; только BOS — осторожно</t>
+          <t>повторяющийся спрос; большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
         </is>
       </c>
       <c r="R2" s="4" t="n">
-        <v>400.4</v>
+        <v>10380</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -7194,34 +7187,34 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>BACN10JR3CFD</t>
+          <t>BACC30BL6</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>NUTPLATE</t>
+          <t>COLLAR</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>3122</v>
+        <v>2000</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>7280</v>
+        <v>14000</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>10380</v>
+        <v>26000</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>87</v>
+        <v>85.7</v>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
@@ -7249,11 +7242,11 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>заметная сумма; большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
         </is>
       </c>
       <c r="R3" s="4" t="n">
-        <v>10380</v>
+        <v>26000</v>
       </c>
       <c r="S3" s="3" t="n">
         <v>0</v>
@@ -7265,34 +7258,34 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>BACR12BU17SN</t>
+          <t>CB6009CR3-1P</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>RING</t>
+          <t>NUTPLATE</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3000</v>
+        <v>1900</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>6.75</v>
+        <v>21.5</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>15.2</v>
+        <v>35.5</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1039.7</v>
+        <v>25128</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>1989.5</v>
+        <v>41416</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>120.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
@@ -7320,11 +7313,11 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая; только BOS — осторожно</t>
+          <t>заметная сумма; большой объём шт; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R4" s="4" t="n">
-        <v>1989.5</v>
+        <v>41416</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>2</v>
@@ -7336,7 +7329,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>BACC30BL6</t>
+          <t>BACC30M6</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -7345,60 +7338,60 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>24000</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>заметная сумма; большой объём шт; заказа не было — зона роста; наценка высокая</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>52000</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>14000</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>26000</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>WENCOR</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>заметная сумма; большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
-        </is>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>26000</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -7407,7 +7400,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>BACR15GF6D10</t>
+          <t>CR3524-6-03</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -7416,60 +7409,60 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1360</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>87400</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>133900</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>повторяющийся спрос; крупная сумма; большой объём шт; заказа не было — зона роста</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>136300</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>PROPONENT</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
-        </is>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -7478,43 +7471,43 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>CB6009CR3-1P</t>
+          <t>HL79-6</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>NUTPLATE</t>
+          <t>THREADED COLLAR PLAIN</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1900</v>
+        <v>1100</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>21.5</v>
+        <v>70</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>35.5</v>
+        <v>125</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>25128</v>
+        <v>7000</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>41416</v>
+        <v>12500</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>78.59999999999999</v>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SATAIR</t>
         </is>
       </c>
       <c r="M7" s="3" t="n">
@@ -7533,14 +7526,14 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>заметная сумма; большой объём шт; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>большой объём шт; заказа не было — зона роста; наценка высокая</t>
         </is>
       </c>
       <c r="R7" s="4" t="n">
-        <v>41416</v>
+        <v>50500</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -7549,43 +7542,43 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>BACS12GP3L15</t>
+          <t>NTA11754-6</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>SCREW</t>
+          <t>COLLAR</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.5</v>
+        <v>26</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.4</v>
+        <v>44</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4200</v>
+        <v>26000</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>9280</v>
+        <v>44000</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>111.7</v>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>69.2</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="M8" s="3" t="n">
@@ -7604,11 +7597,11 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>заметная сумма; большой объём шт; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R8" s="4" t="n">
-        <v>9280</v>
+        <v>44000</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>0</v>
@@ -7620,34 +7613,34 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>BACC30M6</t>
+          <t>CR3213-6-7</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>COLLAR</t>
+          <t>RIVET</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>13000</v>
+        <v>12000</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>84.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -7675,14 +7668,14 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>заметная сумма; большой объём шт; заказа не было — зона роста; наценка высокая</t>
+          <t>заметная сумма; большой объём шт; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R9" s="4" t="n">
-        <v>52000</v>
+        <v>20000</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -7691,7 +7684,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>BACR15GF5D10</t>
+          <t>CR3213-6-6</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -7703,31 +7696,31 @@
         <v>1</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.28</v>
+        <v>11</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.7</v>
+        <v>18</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>420</v>
+        <v>11000</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1050</v>
+        <v>18000</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>63.6</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="M10" s="3" t="n">
@@ -7746,11 +7739,11 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>большой объём шт; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1050</v>
+        <v>18000</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>0</v>
@@ -7762,34 +7755,34 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>BACS12GR3L15</t>
+          <t>CR3213-4-3</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>SCREW</t>
+          <t>RIVET</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1408</v>
+        <v>1000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.5</v>
+        <v>8.75</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3.5</v>
+        <v>16</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3520</v>
+        <v>8750</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4928</v>
+        <v>16000</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>40</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
@@ -7817,11 +7810,11 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка уже ниже; цена с портала</t>
+          <t>большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
         </is>
       </c>
       <c r="R11" s="4" t="n">
-        <v>4928</v>
+        <v>16000</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>0</v>
@@ -7833,7 +7826,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>CR3524-6-03</t>
+          <t>CR3213-4-5</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -7842,25 +7835,25 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1360</v>
+        <v>1000</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>64.5</v>
+        <v>9</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>87400</v>
+        <v>9000</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>133900</v>
+        <v>16000</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>61.4</v>
+        <v>77.8</v>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
@@ -7888,14 +7881,14 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос; крупная сумма; большой объём шт; заказа не было — зона роста</t>
+          <t>большой объём шт; заказа не было — зона роста; наценка высокая</t>
         </is>
       </c>
       <c r="R12" s="4" t="n">
-        <v>136300</v>
+        <v>16000</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7904,7 +7897,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>BACR15BB6AD7C</t>
+          <t>CR3213-5-6</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -7913,34 +7906,34 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1260</v>
+        <v>1000</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3</v>
+        <v>9</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.7</v>
+        <v>16</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>300</v>
+        <v>9000</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>700</v>
+        <v>16000</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>133.3</v>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>77.8</v>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="M13" s="3" t="n">
@@ -7959,14 +7952,14 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>большой объём шт; заказа не было — зона роста; наценка высокая</t>
         </is>
       </c>
       <c r="R13" s="4" t="n">
-        <v>1319.2</v>
+        <v>16000</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7975,43 +7968,43 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>HL79-6</t>
+          <t>CR3212-6-6</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>THREADED COLLAR PLAIN</t>
+          <t>RIVET</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>12500</v>
+        <v>15000</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>78.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>DISTRIBUTOR</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>SATAIR</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="M14" s="3" t="n">
@@ -8034,7 +8027,7 @@
         </is>
       </c>
       <c r="R14" s="4" t="n">
-        <v>50500</v>
+        <v>15000</v>
       </c>
       <c r="S14" s="3" t="n">
         <v>0</v>
@@ -8046,43 +8039,43 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>BACB30NW6K3</t>
+          <t>CR3212-5-4</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>BOLT</t>
+          <t>RIVET</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1088</v>
+        <v>1000</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3300</v>
+        <v>7000</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>6560</v>
+        <v>14000</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>93.3</v>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>100</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="M15" s="3" t="n">
@@ -8101,11 +8094,11 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>большой объём шт; заказа не было — зона роста; наценка высокая</t>
         </is>
       </c>
       <c r="R15" s="4" t="n">
-        <v>6560</v>
+        <v>14000</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>0</v>
@@ -8117,7 +8110,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>NAS1097AD5-14</t>
+          <t>CR3212-6-5</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -8129,31 +8122,31 @@
         <v>1</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1020</v>
+        <v>1000</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1632</v>
+        <v>7000</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3060</v>
+        <v>14000</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>100</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="M16" s="3" t="n">
@@ -8172,14 +8165,14 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая; только BOS — осторожно</t>
+          <t>большой объём шт; заказа не было — зона роста; наценка высокая</t>
         </is>
       </c>
       <c r="R16" s="4" t="n">
-        <v>3060</v>
+        <v>14000</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -8188,43 +8181,43 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>NTA11754-6</t>
+          <t>638060-77453</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>COLLAR</t>
+          <t>CUTTER</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>26000</v>
+        <v>6600</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>44000</v>
+        <v>12600</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>69.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
@@ -8243,11 +8236,11 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>заметная сумма; большой объём шт; заказа не было — зона роста</t>
+          <t>большой объём шт; заказа не было — зона роста; наценка высокая</t>
         </is>
       </c>
       <c r="R17" s="4" t="n">
-        <v>44000</v>
+        <v>12600</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>0</v>
@@ -8259,43 +8252,43 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>CR3213-6-7</t>
+          <t>357484</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>LINING, CERAMETALLIC</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>12</v>
+        <v>142.8</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>12000</v>
+        <v>7282.8</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>20000</v>
+        <v>12240</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>OTHER</t>
+        <v>68.09999999999999</v>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M18" s="3" t="n">
@@ -8314,14 +8307,14 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>заметная сумма; большой объём шт; заказа не было — зона роста</t>
+          <t>большой объём шт; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R18" s="4" t="n">
-        <v>20000</v>
+        <v>12240</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -8330,43 +8323,43 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>CR3213-6-6</t>
+          <t>411N1527-1</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>PAD</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1000</v>
+        <v>344</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>11</v>
+        <v>94.25</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>11000</v>
+        <v>10283</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>18000</v>
+        <v>17448</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>OTHER</t>
+        <v>73.5</v>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M19" s="3" t="n">
@@ -8385,14 +8378,14 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста</t>
+          <t>повторяющийся спрос; заказа не было — зона роста; наценка высокая; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R19" s="4" t="n">
-        <v>18000</v>
+        <v>17448</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -8401,34 +8394,34 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>CR3213-4-3</t>
+          <t>BACB30US9K15</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>BOLT</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>8.75</v>
+        <v>160</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>16</v>
+        <v>260</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>8750</v>
+        <v>16000</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>16000</v>
+        <v>26000</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>82.90000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -8456,11 +8449,11 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="R20" s="4" t="n">
-        <v>16000</v>
+        <v>26000</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>0</v>
@@ -8472,43 +8465,43 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>CR3213-4-5</t>
+          <t>7377543</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>BRAKE LININGS</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>16</v>
+        <v>280</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>9000</v>
+        <v>54000</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>16000</v>
+        <v>84000</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>77.8</v>
+        <v>55.6</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="M21" s="3" t="n">
@@ -8527,11 +8520,11 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая</t>
+          <t>заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R21" s="4" t="n">
-        <v>16000</v>
+        <v>84000</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>0</v>
@@ -8543,43 +8536,43 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>CR3213-5-6</t>
+          <t>357562</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>LINING, CERAMETALLIC</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>9</v>
+        <v>148.33</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>16</v>
+        <v>250</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>9000</v>
+        <v>15129.66</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>16000</v>
+        <v>25500</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>OTHER</t>
+        <v>68.5</v>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M22" s="3" t="n">
@@ -8598,14 +8591,14 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая</t>
+          <t>заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R22" s="4" t="n">
-        <v>16000</v>
+        <v>25500</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -8614,69 +8607,69 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>CR3212-6-6</t>
+          <t>2614478</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>SCREW, MACHINE</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>288</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>29256</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>54617</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>AVIALL</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>часто спрашивают; заметная сумма; заказа не было — зона роста; наценка высокая</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>59657</v>
+      </c>
+      <c r="S23" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>8000</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J23" s="5" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая</t>
-        </is>
-      </c>
-      <c r="R23" s="4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -8685,69 +8678,69 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>CR3212-5-4</t>
+          <t>9109M73P04</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>NUT</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>288</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>2318.4</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>25920</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>1018</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>заметная сумма; заказа не было — зона роста; наценка высокая</t>
+        </is>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>28620</v>
+      </c>
+      <c r="S24" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>7000</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>14000</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая</t>
-        </is>
-      </c>
-      <c r="R24" s="4" t="n">
-        <v>14000</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -8756,43 +8749,43 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>CR3212-6-5</t>
+          <t>FDC6400-14-10T</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>SEAT BELT</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1000</v>
+        <v>252</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>7</v>
+        <v>206.5</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>14</v>
+        <v>325</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>7000</v>
+        <v>31328</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>14000</v>
+        <v>48110</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>OTHER</t>
+        <v>57.8</v>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M25" s="3" t="n">
@@ -8811,14 +8804,14 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая</t>
+          <t>заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R25" s="4" t="n">
-        <v>14000</v>
+        <v>48110</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -8827,43 +8820,43 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>NAS1523AA4R</t>
+          <t>140N2022-1</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>PACKING</t>
+          <t>VALVE ASSY-DRAIN</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1000</v>
+        <v>244</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.8</v>
+        <v>19.375</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3800</v>
+        <v>5537.5</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7000</v>
+        <v>11776</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>102.5</v>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PROPONENT</t>
         </is>
       </c>
       <c r="M26" s="3" t="n">
@@ -8882,14 +8875,14 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая; только BOS — осторожно</t>
+          <t>заказа не было — зона роста; наценка высокая; цена с портала</t>
         </is>
       </c>
       <c r="R26" s="4" t="n">
-        <v>7000</v>
+        <v>11776</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -8898,34 +8891,34 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>BACB30VT6K3</t>
+          <t>7577741</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>BOLT</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1000</v>
+        <v>224</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2</v>
+        <v>23.125</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.8</v>
+        <v>49</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2000</v>
+        <v>5656.25</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>4800</v>
+        <v>10310</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
@@ -8953,11 +8946,11 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>повторяющийся спрос; заказа не было — зона роста; наценка высокая; цена с портала</t>
         </is>
       </c>
       <c r="R27" s="4" t="n">
-        <v>4800</v>
+        <v>10310</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>0</v>
@@ -8969,43 +8962,43 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>BACB30MY6K3</t>
+          <t>2604374</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>BOLT</t>
+          <t>NUT</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.8</v>
+        <v>162</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2000</v>
+        <v>18600</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4800</v>
+        <v>32400</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>140</v>
-      </c>
-      <c r="K28" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>74.2</v>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M28" s="3" t="n">
@@ -9024,14 +9017,14 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>заметная сумма; заказа не было — зона роста; наценка высокая; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R28" s="4" t="n">
-        <v>4800</v>
+        <v>32400</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -9040,43 +9033,43 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>BACR15DR3AC6</t>
+          <t>SG8191-1</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>RIVETS</t>
+          <t>PHOTOLUMINESCENT STRIP</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1000</v>
+        <v>154</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3</v>
+        <v>1968.29</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.8</v>
+        <v>3000</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3000</v>
+        <v>92509.63</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4800</v>
+        <v>141000</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="K29" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>52.4</v>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M29" s="3" t="n">
@@ -9095,14 +9088,14 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; цена с портала</t>
+          <t>крупная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R29" s="4" t="n">
-        <v>4800</v>
+        <v>141000</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -9111,43 +9104,43 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>MS20615-5M12</t>
+          <t>2602540</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>BOLT</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.15</v>
+        <v>210</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4</v>
+        <v>320</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2150</v>
+        <v>31500</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4000</v>
+        <v>48000</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="K30" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>52.4</v>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="M30" s="3" t="n">
@@ -9166,14 +9159,14 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая; только BOS — осторожно</t>
+          <t>заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="R30" s="4" t="n">
-        <v>4000</v>
+        <v>48000</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -9182,43 +9175,43 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>BACC15AJ2</t>
+          <t>217441-0</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>CLIP</t>
+          <t>CARRING BAG</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.3</v>
+        <v>68</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.4</v>
+        <v>98</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1300</v>
+        <v>10200</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3400</v>
+        <v>14700</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>161.5</v>
-      </c>
-      <c r="K31" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>44.1</v>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="M31" s="3" t="n">
@@ -9237,14 +9230,14 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="R31" s="4" t="n">
-        <v>3400</v>
+        <v>14700</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9259,7 +9252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9299,41 +9292,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P/N</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BOS DDP Total excluded</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Portal DDP Total kept</t>
-        </is>
+          <t>BACN11AL1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>834000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BOS suppliers</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Portal suppliers</t>
+          <t>WENCOR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BACN11AL1</t>
+          <t>65C33095-5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>834000</v>
+        <v>40000</v>
       </c>
       <c r="C3" t="n">
-        <v>370</v>
+        <v>14640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -9349,14 +9338,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>65C33095-5</t>
+          <t>113A9309-1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40000</v>
+        <v>35800</v>
       </c>
       <c r="C4" t="n">
-        <v>14640</v>
+        <v>48360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -9372,14 +9361,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>113A9309-1</t>
+          <t>69-41730-64</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35800</v>
+        <v>25600</v>
       </c>
       <c r="C5" t="n">
-        <v>48360</v>
+        <v>7250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -9388,21 +9377,21 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>69-41730-64</t>
+          <t>2100002-01-104</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25600</v>
+        <v>18000</v>
       </c>
       <c r="C6" t="n">
-        <v>7250</v>
+        <v>55220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -9418,14 +9407,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2100002-01-104</t>
+          <t>135-00-279-79CA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18000</v>
+        <v>11520</v>
       </c>
       <c r="C7" t="n">
-        <v>55220</v>
+        <v>870</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -9441,14 +9430,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>135-00-279-79CA</t>
+          <t>SL40359</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11520</v>
+        <v>11280</v>
       </c>
       <c r="C8" t="n">
-        <v>870</v>
+        <v>3600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -9464,14 +9453,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SL40359</t>
+          <t>139-00-240-34</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11280</v>
+        <v>8640</v>
       </c>
       <c r="C9" t="n">
-        <v>3600</v>
+        <v>6615</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -9487,14 +9476,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>139-00-240-34</t>
+          <t>170-14458-990</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8640</v>
+        <v>7270</v>
       </c>
       <c r="C10" t="n">
-        <v>6615</v>
+        <v>3780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -9510,14 +9499,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>170-14458-990</t>
+          <t>411N2599-11C</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7270</v>
+        <v>6450</v>
       </c>
       <c r="C11" t="n">
-        <v>3780</v>
+        <v>1590</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -9533,14 +9522,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>411N2599-11C</t>
+          <t>332A2341-4</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6450</v>
+        <v>5290</v>
       </c>
       <c r="C12" t="n">
-        <v>1590</v>
+        <v>5610</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -9549,21 +9538,21 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>WENCOR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>332A2341-4</t>
+          <t>65-54998-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5290</v>
+        <v>4720</v>
       </c>
       <c r="C13" t="n">
-        <v>5610</v>
+        <v>1980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9579,14 +9568,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>65-54998-17</t>
+          <t>143A8335-1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4720</v>
+        <v>4610</v>
       </c>
       <c r="C14" t="n">
-        <v>1980</v>
+        <v>3480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -9595,21 +9584,21 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>143A8335-1</t>
+          <t>60477</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4610</v>
+        <v>4500</v>
       </c>
       <c r="C15" t="n">
-        <v>3480</v>
+        <v>6420</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -9625,14 +9614,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>60477</t>
+          <t>60476</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4500</v>
+        <v>4060</v>
       </c>
       <c r="C16" t="n">
-        <v>6420</v>
+        <v>3180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -9648,14 +9637,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>60476</t>
+          <t>65-90305-66</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4060</v>
+        <v>3680</v>
       </c>
       <c r="C17" t="n">
-        <v>3180</v>
+        <v>2040</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9664,21 +9653,21 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>WENCOR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>65-90305-66</t>
+          <t>65-90305-58</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3680</v>
+        <v>3240</v>
       </c>
       <c r="C18" t="n">
-        <v>2040</v>
+        <v>2640</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9694,14 +9683,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>65-90305-58</t>
+          <t>BACB30VT6K4</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3240</v>
+        <v>3120</v>
       </c>
       <c r="C19" t="n">
-        <v>2640</v>
+        <v>340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -9710,21 +9699,21 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BACB30VT6K4</t>
+          <t>4663-8</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3120</v>
+        <v>2720</v>
       </c>
       <c r="C20" t="n">
-        <v>340</v>
+        <v>7400</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -9740,14 +9729,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4663-8</t>
+          <t>D72D93003-005</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2720</v>
+        <v>2350</v>
       </c>
       <c r="C21" t="n">
-        <v>7400</v>
+        <v>1310</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -9763,14 +9752,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D72D93003-005</t>
+          <t>411N1527-2</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2350</v>
+        <v>2030</v>
       </c>
       <c r="C22" t="n">
-        <v>1310</v>
+        <v>4100</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -9779,21 +9768,21 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>WENCOR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>411N1527-2</t>
+          <t>65-49571-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2030</v>
+        <v>1920</v>
       </c>
       <c r="C23" t="n">
-        <v>4100</v>
+        <v>600</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -9809,14 +9798,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>65-49571-21</t>
+          <t>S8990-266</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1920</v>
+        <v>1500</v>
       </c>
       <c r="C24" t="n">
-        <v>600</v>
+        <v>826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -9825,21 +9814,21 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S8990-266</t>
+          <t>65-90305-15</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1500</v>
+        <v>1440</v>
       </c>
       <c r="C25" t="n">
-        <v>826</v>
+        <v>5400</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -9848,21 +9837,21 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>WENCOR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>65-90305-15</t>
+          <t>BACR15FT5D10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1440</v>
+        <v>1290</v>
       </c>
       <c r="C26" t="n">
-        <v>5400</v>
+        <v>280</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -9871,21 +9860,21 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BACR15FT5D10</t>
+          <t>J221P906</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1290</v>
+        <v>680</v>
       </c>
       <c r="C27" t="n">
-        <v>280</v>
+        <v>630</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -9894,21 +9883,21 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>WENCOR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>J221P906</t>
+          <t>BACR15BB6AD7C</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>680</v>
+        <v>619.2</v>
       </c>
       <c r="C28" t="n">
-        <v>630</v>
+        <v>700</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -9917,21 +9906,21 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BACR15BB6AD7C</t>
+          <t>BACB30LH3-4</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>619.2</v>
+        <v>584.4</v>
       </c>
       <c r="C29" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -9940,21 +9929,21 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>WENCOR</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BACB30LH3-4</t>
+          <t>BACN10YT4CD</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>584.4</v>
+        <v>576</v>
       </c>
       <c r="C30" t="n">
-        <v>900</v>
+        <v>832</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -9963,21 +9952,21 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BACN10YT4CD</t>
+          <t>65-90305-24</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="C31" t="n">
-        <v>832</v>
+        <v>12610</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -9986,21 +9975,21 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>WENCOR</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>65-90305-24</t>
+          <t>412A1810-3B</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="C32" t="n">
-        <v>12610</v>
+        <v>1009.9</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -10016,14 +10005,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>412A1810-3B</t>
+          <t>3A090-0475</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>560</v>
+        <v>320</v>
       </c>
       <c r="C33" t="n">
-        <v>1009.9</v>
+        <v>624</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -10032,21 +10021,21 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3A090-0475</t>
+          <t>AS3236-14</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="C34" t="n">
-        <v>624</v>
+        <v>280</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -10062,14 +10051,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AS3236-14</t>
+          <t>32757</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="C35" t="n">
-        <v>280</v>
+        <v>488</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -10085,14 +10074,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>32757</t>
+          <t>BACB30NY6K6</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C36" t="n">
-        <v>488</v>
+        <v>800</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -10108,14 +10097,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BACB30NY6K6</t>
+          <t>BACN10JZ3A2CDMU</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C37" t="n">
-        <v>800</v>
+        <v>962</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -10131,14 +10120,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BACN10JZ3A2CDMU</t>
+          <t>BACP11K5</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="C38" t="n">
-        <v>962</v>
+        <v>300</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -10154,14 +10143,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BACP11K5</t>
+          <t>BACN10ZR3CD</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>266</v>
+        <v>260.7</v>
       </c>
       <c r="C39" t="n">
-        <v>300</v>
+        <v>618</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -10170,21 +10159,21 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>WENCOR</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BACN10ZR3CD</t>
+          <t>300-834-044</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>260.7</v>
+        <v>257.4</v>
       </c>
       <c r="C40" t="n">
-        <v>618</v>
+        <v>370</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -10193,21 +10182,21 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>300-834-044</t>
+          <t>VL1002GE1-023</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>257.4</v>
       </c>
       <c r="C41" t="n">
-        <v>370</v>
+        <v>297</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -10223,14 +10212,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>VL1002GE1-023</t>
+          <t>D-150-0180</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>257.4</v>
+        <v>256</v>
       </c>
       <c r="C42" t="n">
-        <v>297</v>
+        <v>910</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -10246,14 +10235,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>D-150-0180</t>
+          <t>AS1895-7-200</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C43" t="n">
-        <v>910</v>
+        <v>840</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -10262,21 +10251,21 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>PROPONENT, WENCOR</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AS1895-7-200</t>
+          <t>MS29513-030</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>255</v>
       </c>
       <c r="C44" t="n">
-        <v>840</v>
+        <v>240</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -10284,29 +10273,6 @@
         </is>
       </c>
       <c r="E44" t="inlineStr">
-        <is>
-          <t>PROPONENT, WENCOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>MS29513-030</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>255</v>
-      </c>
-      <c r="C45" t="n">
-        <v>240</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
         <is>
           <t>PROPONENT</t>
         </is>

--- a/utair_tops_for_client_prices.xlsx
+++ b/utair_tops_for_client_prices.xlsx
@@ -13,14 +13,15 @@
     <sheet name="Top by DDP value" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Top by qty" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="RFQ variant audit" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Universe RFQ&gt;=3 DDP&gt;=10k" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="BOS dropped vs portal" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Universe RFQ&gt;=3 DDP&gt;=10k" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Priority ask client'!$A$1:$S$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Top by requests'!$A$1:$S$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Top by DDP value'!$A$1:$S$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Top by qty'!$A$1:$S$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Universe RFQ&gt;=3 DDP&gt;=10k'!$A$1:$S$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Priority ask client'!$A$1:$T$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Top by requests'!$A$1:$T$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Top by DDP value'!$A$1:$T$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Top by qty'!$A$1:$T$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Universe RFQ&gt;=3 DDP&gt;=10k'!$A$1:$T$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,65 +478,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="115" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>UTAIR EXP — топ с исправлением: 1 RFQ = 1 запрос (колонка Unicode / ExpR)</t>
+          <t>UTAIR EXP sample — RFQ uniqueness + BOS outlier filter vs portal</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНИЕ: несколько строк с одним ExpR и одним P/N = варианты ответа на ОДИН запрос</t>
+          <t>RFQ count = unique ExpR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Пример: 810-2042/K — 3 строки, 1 ExpR26608 → считается как 1 запрос</t>
+          <t>If P/N has PROPONENT/WENCOR price: drop BOS when BOS PE &gt; 1.2x portal PE (or DDP EA &gt;= 1.5x portal)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RFQ count = число уникальных ExpR; Qty/DDP суммируются по 1 представителю на RFQ (приоритет портала)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ФИЛЬТРЫ: RFQ count &gt;= 3; DDP Total &gt;= $10,000; без 90010705-1</t>
+          <t>Example 65C33095-5: WENCOR ~$158-190 kept; BOS $876-980 dropped; DDP Total=$14,640</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Filters: RFQ&gt;=3, DDP&gt;=$10k, exclude 90010705-1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ЦЕНЫ: внутри RFQ выбираем PROPONENT/WENCOR &gt; DISTRIBUTOR &gt; OTHER &gt; BOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Universe: 53 P/N | Variant cases found: 28</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Priority: 94 RFQ, $1,896,197 DDP</t>
+          <t>Universe 51 | BOS drops 37 PNs / $1,047,189</t>
         </is>
       </c>
     </row>
@@ -550,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -571,7 +558,8 @@
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
     <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -667,7 +655,12 @@
       </c>
       <c r="S1" s="2" t="inlineStr">
         <is>
-          <t>DDP if sum all variants</t>
+          <t>DDP raw all rows</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>BOS DDP dropped</t>
         </is>
       </c>
     </row>
@@ -741,6 +734,9 @@
       <c r="S2" s="4" t="n">
         <v>566800</v>
       </c>
+      <c r="T2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -812,6 +808,9 @@
       <c r="S3" s="4" t="n">
         <v>87160</v>
       </c>
+      <c r="T3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -882,6 +881,9 @@
       </c>
       <c r="S4" s="4" t="n">
         <v>59657</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -954,6 +956,9 @@
       <c r="S5" s="4" t="n">
         <v>164800</v>
       </c>
+      <c r="T5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -1025,6 +1030,9 @@
       <c r="S6" s="4" t="n">
         <v>136300</v>
       </c>
+      <c r="T6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -1090,11 +1098,14 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); варианты ответов: 7 строк / 3 RFQ; крупная сумма; заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); варианты: 7 строк / 3 RFQ; крупная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S7" s="4" t="n">
         <v>147740</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1167,6 +1178,9 @@
       <c r="S8" s="4" t="n">
         <v>89900</v>
       </c>
+      <c r="T8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1174,12 +1188,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>113A9309-1</t>
+          <t>67839</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>BUSHING-PIVOT BOLT</t>
+          <t>CARTRIDGE VALVE ASSY</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1192,19 +1206,19 @@
         <v>17</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2810</v>
+        <v>3058.78</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4280</v>
+        <v>4800</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>54420</v>
+        <v>55070.24</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>84160</v>
+        <v>81610</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>52.3</v>
+        <v>56.9</v>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
@@ -1213,7 +1227,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>BOS, WENCOR</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
@@ -1236,7 +1250,10 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>84160</v>
+        <v>81610</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1245,12 +1262,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>67839</t>
+          <t>310A2042-3</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>CARTRIDGE VALVE ASSY</t>
+          <t>PIN</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1260,22 +1277,22 @@
         <v>3</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3058.78</v>
+        <v>5306.25</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4800</v>
+        <v>7700</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>55070.24</v>
+        <v>49237.5</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>81610</v>
+        <v>68250</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>56.9</v>
+        <v>43.1</v>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
@@ -1307,7 +1324,10 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>81610</v>
+        <v>68250</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1316,46 +1336,46 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2100002-01-104</t>
+          <t>90G97</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>RESTRAINT ASSY</t>
+          <t>SWITCH</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4579.5</v>
+        <v>7650</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>7210</v>
+        <v>11400</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>49236</v>
+        <v>43100</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>73220</v>
+        <v>65200</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>52.5</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>BOS, PROPONENT</t>
+          <t>AVIALL, BOS</t>
         </is>
       </c>
       <c r="N11" s="3" t="n">
@@ -1374,11 +1394,14 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>73220</v>
+        <v>65200</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1387,12 +1410,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>310A2042-3</t>
+          <t>2100002-01-104</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>PIN</t>
+          <t>RESTRAINT ASSY</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1402,22 +1425,22 @@
         <v>3</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5306.25</v>
+        <v>4579.5</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7700</v>
+        <v>7005</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>49237.5</v>
+        <v>36636</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>68250</v>
+        <v>55220</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>43.1</v>
+        <v>53</v>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
@@ -1426,7 +1449,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
       <c r="N12" s="3" t="n">
@@ -1445,11 +1468,14 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); BOS отсечён ≈$18,000; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>68250</v>
+        <v>73220</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="13">
@@ -1458,46 +1484,46 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>90G97</t>
+          <t>141A6075-3</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>SWITCH</t>
+          <t>ARM ASSY</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>6</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>7650</v>
+        <v>9537.5</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>11400</v>
+        <v>13800</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>43100</v>
+        <v>38637.5</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>65200</v>
+        <v>55000</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>41.8</v>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>AVIALL, BOS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N13" s="3" t="n">
@@ -1516,11 +1542,14 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>65200</v>
+        <v>55000</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1529,37 +1558,37 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>65C33095-5</t>
+          <t>113A9309-1</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>GASKET</t>
+          <t>BUSHING-PIVOT BOLT</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>533.21</v>
+        <v>2670</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>800</v>
+        <v>4130</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>35870.6</v>
+        <v>30920</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>54640</v>
+        <v>48360</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>65.8</v>
+        <v>54.8</v>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
@@ -1568,7 +1597,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>BOS, WENCOR</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
@@ -1587,11 +1616,14 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); BOS отсечён ≈$35,800; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>54640</v>
+        <v>84160</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>35800</v>
       </c>
     </row>
     <row r="15">
@@ -1664,6 +1696,9 @@
       <c r="S15" s="4" t="n">
         <v>45700</v>
       </c>
+      <c r="T15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1735,6 +1770,9 @@
       <c r="S16" s="4" t="n">
         <v>45700</v>
       </c>
+      <c r="T16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1806,6 +1844,9 @@
       <c r="S17" s="4" t="n">
         <v>33000</v>
       </c>
+      <c r="T17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1877,6 +1918,9 @@
       <c r="S18" s="4" t="n">
         <v>22560</v>
       </c>
+      <c r="T18" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1948,6 +1992,9 @@
       <c r="S19" s="4" t="n">
         <v>19560</v>
       </c>
+      <c r="T19" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1955,12 +2002,12 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>65-90305-88</t>
+          <t>65C33095-5</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>KIT - CFM56-7 FUEL PUMP FILTER</t>
+          <t>GASKET</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1970,31 +2017,31 @@
         <v>4</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>234</v>
+        <v>173.975</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>390</v>
+        <v>295</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>8690</v>
+        <v>8598</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>14350</v>
+        <v>14640</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>69.7</v>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>AVIALL, BOS</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
@@ -2013,11 +2060,14 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); BOS отсечён ≈$40,000; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>14350</v>
+        <v>54640</v>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>40000</v>
       </c>
     </row>
     <row r="21">
@@ -2026,12 +2076,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>BACC30BL8</t>
+          <t>65-90305-88</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>COLLAR</t>
+          <t>KIT - CFM56-7 FUEL PUMP FILTER</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -2041,31 +2091,31 @@
         <v>4</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>690</v>
+        <v>35</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>8</v>
+        <v>234</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>16.7</v>
+        <v>390</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>7520</v>
+        <v>8690</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>13600</v>
+        <v>14350</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>91.90000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>BOS, MARKET</t>
+          <t>AVIALL, BOS</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
@@ -2084,11 +2134,14 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); большой объём шт; заказа не было — зона роста; наценка высокая</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>13600</v>
+        <v>14350</v>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2097,12 +2150,12 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>65-90305-24</t>
+          <t>BACC30BL8</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>FILTER MAINTENANCE KIT</t>
+          <t>COLLAR</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -2112,31 +2165,31 @@
         <v>4</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>26</v>
+        <v>690</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>329.475</v>
+        <v>8</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>545</v>
+        <v>16.7</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>7975.5</v>
+        <v>7520</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>13180</v>
+        <v>13600</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>91.90000000000001</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>BOS, WENCOR</t>
+          <t>BOS, MARKET</t>
         </is>
       </c>
       <c r="N22" s="3" t="n">
@@ -2155,11 +2208,14 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); большой объём шт; заказа не было — зона роста; наценка высокая</t>
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>13180</v>
+        <v>13600</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2168,37 +2224,37 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>BACN10JR3CFD</t>
+          <t>65-90305-24</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>NUTPLATE</t>
+          <t>FILTER MAINTENANCE KIT</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3122</v>
+        <v>26</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.3</v>
+        <v>329.475</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.3</v>
+        <v>545</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>7280</v>
+        <v>7975.5</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>10380</v>
+        <v>13180</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>87</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
@@ -2207,7 +2263,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>BOS, WENCOR</t>
         </is>
       </c>
       <c r="N23" s="3" t="n">
@@ -2226,11 +2282,14 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>10380</v>
+        <v>13180</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2239,37 +2298,37 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>7577741</t>
+          <t>BACN10JR3CFD</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>FILTER</t>
+          <t>NUTPLATE</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>224</v>
+        <v>3122</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>23.125</v>
+        <v>2.3</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>49</v>
+        <v>4.3</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5656.25</v>
+        <v>7280</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>10310</v>
+        <v>10380</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
@@ -2297,11 +2356,14 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>10310</v>
+        <v>10380</v>
+      </c>
+      <c r="T24" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2310,12 +2372,12 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>332A2341-4</t>
+          <t>7577741</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>LINK ASSY</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -2325,22 +2387,22 @@
         <v>4</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>4</v>
+        <v>224</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1200</v>
+        <v>23.125</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1955</v>
+        <v>49</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>6950.51</v>
+        <v>5656.25</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>10900</v>
+        <v>10310</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
@@ -2349,30 +2411,33 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>BOS, WENCOR</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2400</v>
-      </c>
-      <c r="Q25" s="9" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); уже покупали у нас — репер; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; наценка высокая; цена с портала</t>
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>10900</v>
+        <v>10310</v>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2445,9 +2510,12 @@
       <c r="S26" s="4" t="n">
         <v>14220</v>
       </c>
+      <c r="T26" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S26"/>
+  <autoFilter ref="A1:T26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2458,7 +2526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2479,7 +2547,8 @@
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
     <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -2575,7 +2644,12 @@
       </c>
       <c r="S1" s="2" t="inlineStr">
         <is>
-          <t>DDP if sum all variants</t>
+          <t>DDP raw all rows</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>BOS DDP dropped</t>
         </is>
       </c>
     </row>
@@ -2649,6 +2723,9 @@
       <c r="S2" s="4" t="n">
         <v>59657</v>
       </c>
+      <c r="T2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -2720,6 +2797,9 @@
       <c r="S3" s="4" t="n">
         <v>566800</v>
       </c>
+      <c r="T3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -2790,6 +2870,9 @@
       </c>
       <c r="S4" s="4" t="n">
         <v>87160</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2862,6 +2945,9 @@
       <c r="S5" s="4" t="n">
         <v>65200</v>
       </c>
+      <c r="T5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -2869,12 +2955,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>65C33095-5</t>
+          <t>038845-1</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>GASKET</t>
+          <t>BRACKET-MOUNTING</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -2884,22 +2970,22 @@
         <v>4</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>533.21</v>
+        <v>735.265</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>800</v>
+        <v>1215</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>35870.6</v>
+        <v>27492.72</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>54640</v>
+        <v>45700</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>65.8</v>
+        <v>68</v>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
@@ -2908,7 +2994,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>BOS, WENCOR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
       <c r="N6" s="3" t="n">
@@ -2931,7 +3017,10 @@
         </is>
       </c>
       <c r="S6" s="4" t="n">
-        <v>54640</v>
+        <v>45700</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2940,12 +3029,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>038845-1</t>
+          <t>1A296-0217HS</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>BRACKET-MOUNTING</t>
+          <t>COVER-BACK CUSHION</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -2955,22 +3044,22 @@
         <v>4</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>735.265</v>
+        <v>970</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1215</v>
+        <v>1605</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>27492.72</v>
+        <v>13480</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>45700</v>
+        <v>22560</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>68</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
@@ -2979,7 +3068,7 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>AVIALL, PROPONENT</t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
@@ -3002,7 +3091,10 @@
         </is>
       </c>
       <c r="S7" s="4" t="n">
-        <v>45700</v>
+        <v>22560</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3011,12 +3103,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>1A296-0217HS</t>
+          <t>141A6076-1</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>COVER-BACK CUSHION</t>
+          <t>PIN</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -3026,31 +3118,31 @@
         <v>4</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>970</v>
+        <v>1265</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1605</v>
+        <v>1930</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>13480</v>
+        <v>12190.24</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>22560</v>
+        <v>19560</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>54.3</v>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>AVIALL, PROPONENT</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N8" s="3" t="n">
@@ -3069,11 +3161,14 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>22560</v>
+        <v>19560</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3082,12 +3177,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>141A6076-1</t>
+          <t>65C33095-5</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>PIN</t>
+          <t>GASKET</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -3097,31 +3192,31 @@
         <v>4</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1265</v>
+        <v>173.975</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1930</v>
+        <v>295</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>12190.24</v>
+        <v>8598</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>19560</v>
+        <v>14640</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>69.7</v>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
@@ -3140,11 +3235,14 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); BOS отсечён ≈$40,000; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>19560</v>
+        <v>54640</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>40000</v>
       </c>
     </row>
     <row r="10">
@@ -3217,6 +3315,9 @@
       <c r="S10" s="4" t="n">
         <v>14350</v>
       </c>
+      <c r="T10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -3288,6 +3389,9 @@
       <c r="S11" s="4" t="n">
         <v>13600</v>
       </c>
+      <c r="T11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -3359,6 +3463,9 @@
       <c r="S12" s="4" t="n">
         <v>13180</v>
       </c>
+      <c r="T12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -3430,6 +3537,9 @@
       <c r="S13" s="4" t="n">
         <v>11108</v>
       </c>
+      <c r="T13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -3437,12 +3547,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>332A2341-4</t>
+          <t>7577741</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>LINK ASSY</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -3452,22 +3562,22 @@
         <v>4</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>4</v>
+        <v>224</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1200</v>
+        <v>23.125</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1955</v>
+        <v>49</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6950.51</v>
+        <v>5656.25</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>10900</v>
+        <v>10310</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
@@ -3476,30 +3586,33 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>BOS, WENCOR</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2400</v>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); уже покупали у нас — репер; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; наценка высокая; цена с портала</t>
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>10900</v>
+        <v>10310</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3508,46 +3621,46 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>7577741</t>
+          <t>RAA2196-4</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>FILTER</t>
+          <t>SWITCH</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>224</v>
+        <v>6</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>23.125</v>
+        <v>20300</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>49</v>
+        <v>28000</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5656.25</v>
+        <v>121800</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>10310</v>
+        <v>164800</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>104</v>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>37.9</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="N15" s="3" t="n">
@@ -3566,11 +3679,14 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); крупная сумма; заказа не было — зона роста; наценка уже ниже</t>
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>10310</v>
+        <v>164800</v>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3579,12 +3695,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>RAA2196-4</t>
+          <t>CR3524-6-03</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>SWITCH</t>
+          <t>RIVET</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -3594,31 +3710,31 @@
         <v>3</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>6</v>
+        <v>1360</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>20300</v>
+        <v>65</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>28000</v>
+        <v>114</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>121800</v>
+        <v>88820</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>164800</v>
+        <v>136300</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>37.9</v>
+        <v>69</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>DISTRIBUTOR</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>BOS, MARKET</t>
         </is>
       </c>
       <c r="N16" s="3" t="n">
@@ -3637,11 +3753,14 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); крупная сумма; заказа не было — зона роста; наценка уже ниже</t>
+          <t>повторяющийся спрос (≥3 RFQ); крупная сумма; большой объём шт; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>164800</v>
+        <v>136300</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3650,46 +3769,46 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>CR3524-6-03</t>
+          <t>3036376</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>FILTER ELEMENT</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1360</v>
+        <v>48</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>65</v>
+        <v>1710</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>114</v>
+        <v>2400</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>88820</v>
+        <v>75700</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>136300</v>
+        <v>111040</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>69</v>
+        <v>53.2</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>BOS, MARKET</t>
+          <t>AVIALL, SATAIR</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
@@ -3708,11 +3827,14 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); крупная сумма; большой объём шт; заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); варианты: 7 строк / 3 RFQ; крупная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S17" s="4" t="n">
-        <v>136300</v>
+        <v>147740</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3721,46 +3843,46 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>3036376</t>
+          <t>1C7003-3ABE</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FILTER ELEMENT</t>
+          <t>CUSHION</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>48</v>
-      </c>
       <c r="G18" s="4" t="n">
-        <v>1710</v>
+        <v>8704</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2400</v>
+        <v>12400</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>75700</v>
+        <v>63124</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>111040</v>
+        <v>89900</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>42.5</v>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>AVIALL, SATAIR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N18" s="3" t="n">
@@ -3779,11 +3901,14 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); варианты ответов: 7 строк / 3 RFQ; крупная сумма; заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>147740</v>
+        <v>89900</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3792,12 +3917,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>1C7003-3ABE</t>
+          <t>67839</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>CUSHION</t>
+          <t>CARTRIDGE VALVE ASSY</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -3807,31 +3932,31 @@
         <v>3</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>8704</v>
+        <v>3058.78</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>12400</v>
+        <v>4800</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>63124</v>
+        <v>55070.24</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>89900</v>
+        <v>81610</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>56.9</v>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
@@ -3850,11 +3975,14 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>89900</v>
+        <v>81610</v>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3863,12 +3991,12 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>113A9309-1</t>
+          <t>310A2042-3</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>BUSHING-PIVOT BOLT</t>
+          <t>PIN</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -3878,22 +4006,22 @@
         <v>3</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2810</v>
+        <v>5306.25</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>4280</v>
+        <v>7700</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>54420</v>
+        <v>49237.5</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>84160</v>
+        <v>68250</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>52.3</v>
+        <v>43.1</v>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
@@ -3902,7 +4030,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>BOS, WENCOR</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
@@ -3925,7 +4053,10 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>84160</v>
+        <v>68250</v>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3934,12 +4065,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>67839</t>
+          <t>2100002-01-104</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>CARTRIDGE VALVE ASSY</t>
+          <t>RESTRAINT ASSY</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -3949,22 +4080,22 @@
         <v>3</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3058.78</v>
+        <v>4579.5</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>4800</v>
+        <v>7005</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>55070.24</v>
+        <v>36636</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>81610</v>
+        <v>55220</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>56.9</v>
+        <v>53</v>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
@@ -3973,7 +4104,7 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
@@ -3992,11 +4123,14 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); BOS отсечён ≈$18,000; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>81610</v>
+        <v>73220</v>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="22">
@@ -4005,12 +4139,12 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>2100002-01-104</t>
+          <t>141A6075-3</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>RESTRAINT ASSY</t>
+          <t>ARM ASSY</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -4020,31 +4154,31 @@
         <v>3</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>4579.5</v>
+        <v>9537.5</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>7210</v>
+        <v>13800</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>49236</v>
+        <v>38637.5</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>73220</v>
+        <v>55000</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>41.8</v>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>BOS, PROPONENT</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N22" s="3" t="n">
@@ -4063,11 +4197,14 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>73220</v>
+        <v>55000</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -4076,12 +4213,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>310A2042-3</t>
+          <t>113A9309-1</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>PIN</t>
+          <t>BUSHING-PIVOT BOLT</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -4091,22 +4228,22 @@
         <v>3</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>5306.25</v>
+        <v>2670</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>7700</v>
+        <v>4130</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>49237.5</v>
+        <v>30920</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>68250</v>
+        <v>48360</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>43.1</v>
+        <v>54.8</v>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
@@ -4134,11 +4271,14 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); BOS отсечён ≈$35,800; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>68250</v>
+        <v>84160</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>35800</v>
       </c>
     </row>
     <row r="24">
@@ -4147,12 +4287,12 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>141A6075-3</t>
+          <t>310A2029-11</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>ARM ASSY</t>
+          <t>BOLT-SPECIAL</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -4162,22 +4302,22 @@
         <v>3</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>9537.5</v>
+        <v>1822.1</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>13800</v>
+        <v>2300</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>38637.5</v>
+        <v>32496.8</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>55000</v>
+        <v>45710</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>41.8</v>
+        <v>52.4</v>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
@@ -4209,7 +4349,10 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>55000</v>
+        <v>45710</v>
+      </c>
+      <c r="T24" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -4218,12 +4361,12 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>310A2029-11</t>
+          <t>1024366-311BHV</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>BOLT-SPECIAL</t>
+          <t>BUMPER-ENDBAY</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -4233,31 +4376,31 @@
         <v>3</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1822.1</v>
+        <v>270</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2300</v>
+        <v>480</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>32496.8</v>
+        <v>33300</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>45710</v>
+        <v>45700</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>63.9</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BOS, SATAIR</t>
         </is>
       </c>
       <c r="N25" s="3" t="n">
@@ -4276,11 +4419,14 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>45710</v>
+        <v>45700</v>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -4289,12 +4435,12 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>1024366-311BHV</t>
+          <t>815523-1</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>BUMPER-ENDBAY</t>
+          <t>PACKING</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -4304,31 +4450,31 @@
         <v>3</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>270</v>
+        <v>1320</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>480</v>
+        <v>2010</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>33300</v>
+        <v>30135</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>45700</v>
+        <v>44810</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>52.3</v>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>BOS, SATAIR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
@@ -4347,15 +4493,18 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>45700</v>
+        <v>44810</v>
+      </c>
+      <c r="T26" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S26"/>
+  <autoFilter ref="A1:T26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4366,7 +4515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4387,7 +4536,8 @@
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
     <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -4483,7 +4633,12 @@
       </c>
       <c r="S1" s="2" t="inlineStr">
         <is>
-          <t>DDP if sum all variants</t>
+          <t>DDP raw all rows</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>BOS DDP dropped</t>
         </is>
       </c>
     </row>
@@ -4557,6 +4712,9 @@
       <c r="S2" s="4" t="n">
         <v>566800</v>
       </c>
+      <c r="T2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -4628,6 +4786,9 @@
       <c r="S3" s="4" t="n">
         <v>164800</v>
       </c>
+      <c r="T3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -4698,6 +4859,9 @@
       </c>
       <c r="S4" s="4" t="n">
         <v>136300</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4764,11 +4928,14 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); варианты ответов: 7 строк / 3 RFQ; крупная сумма; заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); варианты: 7 строк / 3 RFQ; крупная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S5" s="4" t="n">
         <v>147740</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4841,6 +5008,9 @@
       <c r="S6" s="4" t="n">
         <v>89900</v>
       </c>
+      <c r="T6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -4912,6 +5082,9 @@
       <c r="S7" s="4" t="n">
         <v>87160</v>
       </c>
+      <c r="T7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -4919,12 +5092,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>113A9309-1</t>
+          <t>67839</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>BUSHING-PIVOT BOLT</t>
+          <t>CARTRIDGE VALVE ASSY</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -4937,19 +5110,19 @@
         <v>17</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2810</v>
+        <v>3058.78</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4280</v>
+        <v>4800</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>54420</v>
+        <v>55070.24</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>84160</v>
+        <v>81610</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>52.3</v>
+        <v>56.9</v>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
@@ -4958,7 +5131,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>BOS, WENCOR</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="N8" s="3" t="n">
@@ -4981,7 +5154,10 @@
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>84160</v>
+        <v>81610</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4990,12 +5166,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>67839</t>
+          <t>310A2042-3</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>CARTRIDGE VALVE ASSY</t>
+          <t>PIN</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -5005,22 +5181,22 @@
         <v>3</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3058.78</v>
+        <v>5306.25</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4800</v>
+        <v>7700</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>55070.24</v>
+        <v>49237.5</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>81610</v>
+        <v>68250</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>56.9</v>
+        <v>43.1</v>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
@@ -5052,7 +5228,10 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>81610</v>
+        <v>68250</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5061,46 +5240,46 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2100002-01-104</t>
+          <t>90G97</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>RESTRAINT ASSY</t>
+          <t>SWITCH</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4579.5</v>
+        <v>7650</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>7210</v>
+        <v>11400</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>49236</v>
+        <v>43100</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>73220</v>
+        <v>65200</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>52.5</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>BOS, PROPONENT</t>
+          <t>AVIALL, BOS</t>
         </is>
       </c>
       <c r="N10" s="3" t="n">
@@ -5119,11 +5298,14 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>73220</v>
+        <v>65200</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5132,46 +5314,46 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>310A2042-3</t>
+          <t>2614478</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>PIN</t>
+          <t>SCREW, MACHINE</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>9</v>
+        <v>288</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5306.25</v>
+        <v>106</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>7700</v>
+        <v>205</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>49237.5</v>
+        <v>32304</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>68250</v>
+        <v>59657</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>78.8</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>AVIALL, BOS</t>
         </is>
       </c>
       <c r="N11" s="3" t="n">
@@ -5190,11 +5372,14 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>часто спрашивают; заметная сумма; заказа не было — зона роста; наценка высокая</t>
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>68250</v>
+        <v>59657</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5203,46 +5388,46 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>90G97</t>
+          <t>2100002-01-104</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>SWITCH</t>
+          <t>RESTRAINT ASSY</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7650</v>
+        <v>4579.5</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>11400</v>
+        <v>7005</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>43100</v>
+        <v>36636</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>65200</v>
+        <v>55220</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>53</v>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>AVIALL, BOS</t>
+          <t>PROPONENT</t>
         </is>
       </c>
       <c r="N12" s="3" t="n">
@@ -5261,11 +5446,14 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); BOS отсечён ≈$18,000; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>65200</v>
+        <v>73220</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="13">
@@ -5274,46 +5462,46 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2614478</t>
+          <t>141A6075-3</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>SCREW, MACHINE</t>
+          <t>ARM ASSY</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>288</v>
+        <v>6</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>106</v>
+        <v>9537.5</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>205</v>
+        <v>13800</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>32304</v>
+        <v>38637.5</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>59657</v>
+        <v>55000</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>41.8</v>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>AVIALL, BOS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N13" s="3" t="n">
@@ -5332,11 +5520,14 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>часто спрашивают; заметная сумма; заказа не было — зона роста; наценка высокая</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>59657</v>
+        <v>55000</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5345,12 +5536,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>141A6075-3</t>
+          <t>113A9309-1</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>ARM ASSY</t>
+          <t>BUSHING-PIVOT BOLT</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -5360,31 +5551,31 @@
         <v>3</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>9537.5</v>
+        <v>2670</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>13800</v>
+        <v>4130</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>38637.5</v>
+        <v>30920</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>55000</v>
+        <v>48360</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>54.8</v>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
@@ -5403,11 +5594,14 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); BOS отсечён ≈$35,800; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>55000</v>
+        <v>84160</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>35800</v>
       </c>
     </row>
     <row r="15">
@@ -5416,46 +5610,46 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>65C33095-5</t>
+          <t>310A2029-11</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>GASKET</t>
+          <t>BOLT-SPECIAL</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>533.21</v>
+        <v>1822.1</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>800</v>
+        <v>2300</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>35870.6</v>
+        <v>32496.8</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>54640</v>
+        <v>45710</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>52.4</v>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>BOS, WENCOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N15" s="3" t="n">
@@ -5474,11 +5668,14 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>54640</v>
+        <v>45710</v>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5487,46 +5684,46 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>310A2029-11</t>
+          <t>038845-1</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>BOLT-SPECIAL</t>
+          <t>BRACKET-MOUNTING</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1822.1</v>
+        <v>735.265</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2300</v>
+        <v>1215</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>32496.8</v>
+        <v>27492.72</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>45710</v>
+        <v>45700</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="L16" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>68</v>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PROPONENT</t>
         </is>
       </c>
       <c r="N16" s="3" t="n">
@@ -5545,11 +5742,14 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>45710</v>
+        <v>45700</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5558,46 +5758,46 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>038845-1</t>
+          <t>1024366-311BHV</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>BRACKET-MOUNTING</t>
+          <t>BUMPER-ENDBAY</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>735.265</v>
+        <v>270</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1215</v>
+        <v>480</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>27492.72</v>
+        <v>33300</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>45700</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>63.9</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>BOS, SATAIR</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
@@ -5616,11 +5816,14 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S17" s="4" t="n">
         <v>45700</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5629,12 +5832,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>1024366-311BHV</t>
+          <t>815523-1</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>BUMPER-ENDBAY</t>
+          <t>PACKING</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -5644,31 +5847,31 @@
         <v>3</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>270</v>
+        <v>1320</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>480</v>
+        <v>2010</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>33300</v>
+        <v>30135</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>45700</v>
+        <v>44810</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>52.3</v>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>BOS, SATAIR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N18" s="3" t="n">
@@ -5687,11 +5890,14 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>45700</v>
+        <v>44810</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5700,12 +5906,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>815523-1</t>
+          <t>2100002-01-129</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>PACKING</t>
+          <t>RESTRAINT SYSTEM - SYS</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -5715,31 +5921,31 @@
         <v>3</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1320</v>
+        <v>5544.53</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2010</v>
+        <v>8200</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>30135</v>
+        <v>22178.12</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>44810</v>
+        <v>33000</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>47.9</v>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PROPONENT</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
@@ -5758,11 +5964,14 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>44810</v>
+        <v>33000</v>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -5771,12 +5980,12 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>2100002-01-129</t>
+          <t>340-007-203-0</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>RESTRAINT SYSTEM - SYS</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -5789,28 +5998,28 @@
         <v>4</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>5544.53</v>
+        <v>5686</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>8200</v>
+        <v>8400</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>22178.12</v>
+        <v>18738</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>33000</v>
+        <v>27960</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>51.2</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>BOS, ENGINE</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
@@ -5829,11 +6038,14 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>33000</v>
+        <v>27960</v>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -5842,12 +6054,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>340-007-203-0</t>
+          <t>332A2930-90</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>BRACKET ASSY</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -5857,31 +6069,31 @@
         <v>3</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>5686</v>
+        <v>5500</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>8400</v>
+        <v>8100</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>18738</v>
+        <v>18100</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>27960</v>
+        <v>26100</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>43.1</v>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>BOS, ENGINE</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
@@ -5900,11 +6112,14 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>27960</v>
+        <v>26100</v>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -5913,12 +6128,12 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>332A2930-90</t>
+          <t>65-0028-11</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>BRACKET ASSY</t>
+          <t>LIGHT</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -5928,31 +6143,31 @@
         <v>3</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>5500</v>
+        <v>2890</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>8100</v>
+        <v>4550</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>18100</v>
+        <v>17340</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>26100</v>
+        <v>25800</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
+        <v>57.4</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="N22" s="3" t="n">
@@ -5971,11 +6186,14 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>26100</v>
+        <v>25800</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -5984,46 +6202,46 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>65-0028-11</t>
+          <t>1A296-0217HS</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>LIGHT</t>
+          <t>COVER-BACK CUSHION</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2890</v>
+        <v>970</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4550</v>
+        <v>1605</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>17340</v>
+        <v>13480</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>25800</v>
+        <v>22560</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>65.59999999999999</v>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>AVIALL, PROPONENT</t>
         </is>
       </c>
       <c r="N23" s="3" t="n">
@@ -6042,11 +6260,14 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>25800</v>
+        <v>22560</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -6055,37 +6276,37 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>1A296-0217HS</t>
+          <t>778000</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>COVER-BACK CUSHION</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>4</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>970</v>
+        <v>189.95</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1605</v>
+        <v>320</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>13480</v>
+        <v>12087.45</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>22560</v>
+        <v>20670</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>65.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
@@ -6094,7 +6315,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>AVIALL, PROPONENT</t>
+          <t>PROPONENT, WENCOR</t>
         </is>
       </c>
       <c r="N24" s="3" t="n">
@@ -6113,11 +6334,14 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); варианты: 4 строк / 3 RFQ; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>22560</v>
+        <v>21410</v>
+      </c>
+      <c r="T24" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -6126,46 +6350,46 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>778000</t>
+          <t>5011211</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>FILTER</t>
+          <t>PIN INDICATOR</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>189.95</v>
+        <v>490</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>320</v>
+        <v>800</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>12087.45</v>
+        <v>12740</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>20670</v>
+        <v>19920</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>PROPONENT/WENCOR</t>
+        <v>63.3</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>PROPONENT, WENCOR</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="N25" s="3" t="n">
@@ -6184,11 +6408,14 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); варианты ответов: 4 строк / 3 RFQ; заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>21410</v>
+        <v>19920</v>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -6197,46 +6424,46 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>5011211</t>
+          <t>141A6076-1</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>PIN INDICATOR</t>
+          <t>PIN</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>490</v>
+        <v>1265</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>800</v>
+        <v>1930</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>12740</v>
+        <v>12190.24</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>19920</v>
+        <v>19560</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
+        <v>54.3</v>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
@@ -6255,15 +6482,18 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>19920</v>
+        <v>19560</v>
+      </c>
+      <c r="T26" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S26"/>
+  <autoFilter ref="A1:T26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6274,7 +6504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6295,7 +6525,8 @@
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
     <col width="34" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -6391,7 +6622,12 @@
       </c>
       <c r="S1" s="2" t="inlineStr">
         <is>
-          <t>DDP if sum all variants</t>
+          <t>DDP raw all rows</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>BOS DDP dropped</t>
         </is>
       </c>
     </row>
@@ -6465,6 +6701,9 @@
       <c r="S2" s="4" t="n">
         <v>10380</v>
       </c>
+      <c r="T2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -6536,6 +6775,9 @@
       <c r="S3" s="4" t="n">
         <v>136300</v>
       </c>
+      <c r="T3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -6606,6 +6848,9 @@
       </c>
       <c r="S4" s="4" t="n">
         <v>13600</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -6678,6 +6923,9 @@
       <c r="S5" s="4" t="n">
         <v>17448</v>
       </c>
+      <c r="T5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -6749,6 +6997,9 @@
       <c r="S6" s="4" t="n">
         <v>59657</v>
       </c>
+      <c r="T6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -6820,6 +7071,9 @@
       <c r="S7" s="4" t="n">
         <v>10310</v>
       </c>
+      <c r="T7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -6891,6 +7145,9 @@
       <c r="S8" s="4" t="n">
         <v>17200</v>
       </c>
+      <c r="T8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -6962,6 +7219,9 @@
       <c r="S9" s="4" t="n">
         <v>10405</v>
       </c>
+      <c r="T9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -7033,6 +7293,9 @@
       <c r="S10" s="4" t="n">
         <v>45700</v>
       </c>
+      <c r="T10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -7058,19 +7321,19 @@
         <v>105</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>533.21</v>
+        <v>173.975</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>800</v>
+        <v>295</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>35870.6</v>
+        <v>8598</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>54640</v>
+        <v>14640</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>65.8</v>
+        <v>69.7</v>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
@@ -7079,7 +7342,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>BOS, WENCOR</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="N11" s="3" t="n">
@@ -7098,11 +7361,14 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); BOS отсечён ≈$40,000; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S11" s="4" t="n">
         <v>54640</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>40000</v>
       </c>
     </row>
     <row r="12">
@@ -7175,6 +7441,9 @@
       <c r="S12" s="4" t="n">
         <v>10200</v>
       </c>
+      <c r="T12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -7246,6 +7515,9 @@
       <c r="S13" s="4" t="n">
         <v>566800</v>
       </c>
+      <c r="T13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -7311,11 +7583,14 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); варианты ответов: 4 строк / 3 RFQ; заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); варианты: 4 строк / 3 RFQ; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S14" s="4" t="n">
         <v>21410</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -7388,6 +7663,9 @@
       <c r="S15" s="4" t="n">
         <v>14210</v>
       </c>
+      <c r="T15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -7453,11 +7731,14 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); варианты ответов: 7 строк / 3 RFQ; крупная сумма; заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); варианты: 7 строк / 3 RFQ; крупная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S16" s="4" t="n">
         <v>147740</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -7530,6 +7811,9 @@
       <c r="S17" s="4" t="n">
         <v>45700</v>
       </c>
+      <c r="T17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -7601,6 +7885,9 @@
       <c r="S18" s="4" t="n">
         <v>14350</v>
       </c>
+      <c r="T18" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -7672,6 +7959,9 @@
       <c r="S19" s="4" t="n">
         <v>44810</v>
       </c>
+      <c r="T19" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -7743,6 +8033,9 @@
       <c r="S20" s="4" t="n">
         <v>14684</v>
       </c>
+      <c r="T20" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -7814,6 +8107,9 @@
       <c r="S21" s="4" t="n">
         <v>19920</v>
       </c>
+      <c r="T21" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -7885,6 +8181,9 @@
       <c r="S22" s="4" t="n">
         <v>13180</v>
       </c>
+      <c r="T22" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -7913,16 +8212,16 @@
         <v>4579.5</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>7210</v>
+        <v>7005</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>49236</v>
+        <v>36636</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>73220</v>
+        <v>55220</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>48.5</v>
+        <v>53</v>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
@@ -7931,7 +8230,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>BOS, PROPONENT</t>
+          <t>PROPONENT</t>
         </is>
       </c>
       <c r="N23" s="3" t="n">
@@ -7950,11 +8249,14 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); BOS отсечён ≈$18,000; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S23" s="4" t="n">
         <v>73220</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="24">
@@ -8027,6 +8329,9 @@
       <c r="S24" s="4" t="n">
         <v>45710</v>
       </c>
+      <c r="T24" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -8098,6 +8403,9 @@
       <c r="S25" s="4" t="n">
         <v>19560</v>
       </c>
+      <c r="T25" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -8169,9 +8477,12 @@
       <c r="S26" s="4" t="n">
         <v>14220</v>
       </c>
+      <c r="T26" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S26"/>
+  <autoFilter ref="A1:T26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8183,15 +8494,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
@@ -8216,12 +8519,12 @@
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>Extra variants</t>
+          <t>Extra</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>ExpR breakdown</t>
+          <t>Breakdown</t>
         </is>
       </c>
     </row>
@@ -8964,12 +9267,1062 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
+          <t>P/N</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Portal PE med</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Portal DDP EA med</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>BOS DDP dropped</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Kept DDP</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>RFQs</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BACN11AL1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>834000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>370</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>[{'expr': '137', 'pe': 2732.4, 'ce': 4170.0, 'ct': 834000.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>65C33095-5</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>173.975</v>
+      </c>
+      <c r="C3" t="n">
+        <v>295</v>
+      </c>
+      <c r="D3" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>14640</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR21067', 'pe': 980.0, 'ce': 1600.0, 'ct': 1600.0}, {'expr': 'ExpR23848', 'pe': 876.42, 'ce': 1280.0, 'ct': 38400.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>113A9309-1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2670</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4130</v>
+      </c>
+      <c r="D4" t="n">
+        <v>35800</v>
+      </c>
+      <c r="E4" t="n">
+        <v>48360</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR22906', 'pe': 4700.0, 'ce': 7160.0, 'ct': 35800.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>69-41730-64</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4760</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7250</v>
+      </c>
+      <c r="D5" t="n">
+        <v>25600</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7250</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR24351', 'pe': 9300.0, 'ce': 12800.0, 'ct': 25600.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2100002-01-104</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4579.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7005</v>
+      </c>
+      <c r="D6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>55220</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR20816', 'pe': 6300.0, 'ce': 9000.0, 'ct': 18000.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>135-00-279-79CA</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>530</v>
+      </c>
+      <c r="C7" t="n">
+        <v>870</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11520</v>
+      </c>
+      <c r="E7" t="n">
+        <v>870</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR25003', 'pe': 833.55, 'ce': 1280.0, 'ct': 11520.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SL40359</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>430</v>
+      </c>
+      <c r="C8" t="n">
+        <v>720</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11280</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR26635', 'pe': 630.74, 'ce': 940.0, 'ct': 11280.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>139-00-240-34</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>109</v>
+      </c>
+      <c r="C9" t="n">
+        <v>189</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8640</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6615</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR23702', 'pe': 145.83, 'ce': 240.0, 'ct': 8640.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>170-14458-990</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2480</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3780</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7270</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3780</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR24413', 'pe': 4774.0, 'ce': 7270.0, 'ct': 7270.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>411N2599-11C</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>320</v>
+      </c>
+      <c r="C11" t="n">
+        <v>530</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6450</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1590</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR24238', 'pe': 810.0, 'ce': 1320.0, 'ct': 3960.0}, {'expr': 'ExpR25132', 'pe': 504.0, 'ce': 830.0, 'ct': 2490.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>332A2341-4</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1830</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5290</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5610</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR24118', 'pe': 3470.51, 'ce': 5290.0, 'ct': 5290.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>65-54998-17</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>391</v>
+      </c>
+      <c r="C13" t="n">
+        <v>660</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4720</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR19143', 'pe': 720.0, 'ce': 1180.0, 'ct': 4720.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>143A8335-1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2280</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3480</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4610</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3480</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR26555', 'pe': 3024.0, 'ce': 4610.0, 'ct': 4610.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>60477</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>951</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1605</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6420</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR25449', 'pe': 1471.8, 'ce': 2250.0, 'ct': 4500.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>60476</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>910</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1590</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4060</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4540</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR25450', 'pe': 1331.29, 'ce': 2030.0, 'ct': 4060.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>65-90305-66</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>310</v>
+      </c>
+      <c r="C17" t="n">
+        <v>510</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3680</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5040</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR21758', 'pe': 560.0, 'ce': 920.0, 'ct': 3680.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>65-90305-58</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>32.475</v>
+      </c>
+      <c r="C18" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3240</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2640</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR21755', 'pe': 62.0, 'ce': 108.0, 'ct': 3240.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BACB30VT6K4</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3120</v>
+      </c>
+      <c r="E19" t="n">
+        <v>340</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR21558', 'pe': 4.2, 'ce': 7.8, 'ct': 3120.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>D72D93003-005</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>800</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1310</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2350</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1310</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR22087', 'pe': 1540.0, 'ce': 2350.0, 'ct': 2350.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>411N1527-2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>47</v>
+      </c>
+      <c r="C21" t="n">
+        <v>82</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4100</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR25510', 'pe': 68.69, 'ce': 120.0, 'ct': 1440.0}, {'expr': 'ExpR26753', 'pe': 68.04, 'ce': 118.0, 'ct': 590.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>65-49571-21</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>60</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1920</v>
+      </c>
+      <c r="E22" t="n">
+        <v>600</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR24950', 'pe': 55.28, 'ce': 96.0, 'ct': 1920.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S8990-266</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>61</v>
+      </c>
+      <c r="C23" t="n">
+        <v>140</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E23" t="n">
+        <v>826</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR25455', 'pe': 86.18, 'ce': 150.0, 'ct': 1500.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>65-90305-15</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>160</v>
+      </c>
+      <c r="C24" t="n">
+        <v>270</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1440</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5400</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR21756', 'pe': 221.0, 'ce': 360.0, 'ct': 1440.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BACR15FT5D10</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1290</v>
+      </c>
+      <c r="E25" t="n">
+        <v>280</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR18852', 'pe': 2.3, 'ce': 4.3, 'ct': 1290.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>J221P906</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>680</v>
+      </c>
+      <c r="E26" t="n">
+        <v>630</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR22605', 'pe': 100.0, 'ce': 170.0, 'ct': 680.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BACR15BB6AD7C</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>619.2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>700</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR20750', 'pe': 2.3, 'ce': 4.3, 'ct': 619.2}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BACB30LH3-4</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>9</v>
+      </c>
+      <c r="D28" t="n">
+        <v>584.4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>900</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR20317', 'pe': 9.2, 'ce': 22.2, 'ct': 266.4}, {'expr': 'ExpR20917', 'pe': 8.0, 'ce': 15.9, 'ct': 318.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>412A1810-3B</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="C29" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="D29" t="n">
+        <v>560</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1009.9</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR22874', 'pe': 32.0, 'ce': 56.0, 'ct': 560.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3A090-0475</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>77</v>
+      </c>
+      <c r="C30" t="n">
+        <v>156</v>
+      </c>
+      <c r="D30" t="n">
+        <v>320</v>
+      </c>
+      <c r="E30" t="n">
+        <v>624</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR19555', 'pe': 154.0, 'ce': 320.0, 'ct': 320.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AS3236-14</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="C31" t="n">
+        <v>14</v>
+      </c>
+      <c r="D31" t="n">
+        <v>308</v>
+      </c>
+      <c r="E31" t="n">
+        <v>280</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR20655', 'pe': 20.68, 'ce': 44.0, 'ct': 308.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BACP11K5</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>266</v>
+      </c>
+      <c r="E32" t="n">
+        <v>300</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>[{'expr': '11', 'pe': 5.44, 'ce': 13.3, 'ct': 266.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BACN10ZR3CD</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="C33" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>260.7</v>
+      </c>
+      <c r="E33" t="n">
+        <v>618</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR22923', 'pe': 9.5, 'ce': 23.7, 'ct': 260.7}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>300-834-044</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D34" t="n">
+        <v>257.4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>370</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR19557', 'pe': 3.9, 'ce': 9.9, 'ct': 257.4}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>VL1002GE1-023</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D35" t="n">
+        <v>257.4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>297</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR21759', 'pe': 2.6, 'ce': 6.6, 'ct': 257.4}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>D-150-0180</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="C36" t="n">
+        <v>49</v>
+      </c>
+      <c r="D36" t="n">
+        <v>256</v>
+      </c>
+      <c r="E36" t="n">
+        <v>910</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>[{'expr': '80', 'pe': 50.0, 'ce': 128.0, 'ct': 256.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AS1895-7-200</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>21.475</v>
+      </c>
+      <c r="C37" t="n">
+        <v>43</v>
+      </c>
+      <c r="D37" t="n">
+        <v>255</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1380</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>[{'expr': 'ExpR25466', 'pe': 32.92, 'ce': 85.0, 'ct': 255.0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MS29513-030</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D38" t="n">
+        <v>255</v>
+      </c>
+      <c r="E38" t="n">
+        <v>240</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>[{'expr': '116', 'pe': 2.0, 'ce': 5.1, 'ct': 255.0}]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
           <t>Rank</t>
         </is>
       </c>
@@ -9060,7 +10413,12 @@
       </c>
       <c r="S1" s="10" t="inlineStr">
         <is>
-          <t>DDP if sum all variants</t>
+          <t>DDP raw all rows</t>
+        </is>
+      </c>
+      <c r="T1" s="10" t="inlineStr">
+        <is>
+          <t>BOS DDP dropped</t>
         </is>
       </c>
     </row>
@@ -9134,6 +10492,9 @@
       <c r="S2" t="n">
         <v>59657</v>
       </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -9205,6 +10566,9 @@
       <c r="S3" t="n">
         <v>566800</v>
       </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9275,6 +10639,9 @@
       </c>
       <c r="S4" t="n">
         <v>87160</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -9347,6 +10714,9 @@
       <c r="S5" t="n">
         <v>65200</v>
       </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -9354,12 +10724,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>65C33095-5</t>
+          <t>038845-1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GASKET</t>
+          <t>BRACKET-MOUNTING</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -9369,22 +10739,22 @@
         <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>533.21</v>
+        <v>735.265</v>
       </c>
       <c r="H6" t="n">
-        <v>800</v>
+        <v>1215</v>
       </c>
       <c r="I6" t="n">
-        <v>35870.6</v>
+        <v>27492.72</v>
       </c>
       <c r="J6" t="n">
-        <v>54640</v>
+        <v>45700</v>
       </c>
       <c r="K6" t="n">
-        <v>65.8</v>
+        <v>68</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -9393,7 +10763,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>BOS, WENCOR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -9416,7 +10786,10 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>54640</v>
+        <v>45700</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9425,12 +10798,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>038845-1</t>
+          <t>1A296-0217HS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BRACKET-MOUNTING</t>
+          <t>COVER-BACK CUSHION</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -9440,22 +10813,22 @@
         <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>735.265</v>
+        <v>970</v>
       </c>
       <c r="H7" t="n">
-        <v>1215</v>
+        <v>1605</v>
       </c>
       <c r="I7" t="n">
-        <v>27492.72</v>
+        <v>13480</v>
       </c>
       <c r="J7" t="n">
-        <v>45700</v>
+        <v>22560</v>
       </c>
       <c r="K7" t="n">
-        <v>68</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -9464,7 +10837,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>AVIALL, PROPONENT</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -9487,7 +10860,10 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>45700</v>
+        <v>22560</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9496,12 +10872,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1A296-0217HS</t>
+          <t>141A6076-1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>COVER-BACK CUSHION</t>
+          <t>PIN</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -9511,31 +10887,31 @@
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>970</v>
+        <v>1265</v>
       </c>
       <c r="H8" t="n">
-        <v>1605</v>
+        <v>1930</v>
       </c>
       <c r="I8" t="n">
-        <v>13480</v>
+        <v>12190.24</v>
       </c>
       <c r="J8" t="n">
-        <v>22560</v>
+        <v>19560</v>
       </c>
       <c r="K8" t="n">
-        <v>65.59999999999999</v>
+        <v>54.3</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PROPONENT/WENCOR</t>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>AVIALL, PROPONENT</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -9554,11 +10930,14 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>22560</v>
+        <v>19560</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -9567,12 +10946,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>141A6076-1</t>
+          <t>65C33095-5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PIN</t>
+          <t>GASKET</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -9582,31 +10961,31 @@
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="G9" t="n">
-        <v>1265</v>
+        <v>173.975</v>
       </c>
       <c r="H9" t="n">
-        <v>1930</v>
+        <v>295</v>
       </c>
       <c r="I9" t="n">
-        <v>12190.24</v>
+        <v>8598</v>
       </c>
       <c r="J9" t="n">
-        <v>19560</v>
+        <v>14640</v>
       </c>
       <c r="K9" t="n">
-        <v>54.3</v>
+        <v>69.7</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>BOS_ONLY</t>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -9625,11 +11004,14 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); BOS отсечён ≈$40,000; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>19560</v>
+        <v>54640</v>
+      </c>
+      <c r="T9" t="n">
+        <v>40000</v>
       </c>
     </row>
     <row r="10">
@@ -9702,6 +11084,9 @@
       <c r="S10" t="n">
         <v>14350</v>
       </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9773,6 +11158,9 @@
       <c r="S11" t="n">
         <v>13600</v>
       </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9844,6 +11232,9 @@
       <c r="S12" t="n">
         <v>13180</v>
       </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9915,6 +11306,9 @@
       <c r="S13" t="n">
         <v>11108</v>
       </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9922,12 +11316,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>332A2341-4</t>
+          <t>7577741</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LINK ASSY</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -9937,22 +11331,22 @@
         <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>224</v>
       </c>
       <c r="G14" t="n">
-        <v>1200</v>
+        <v>23.125</v>
       </c>
       <c r="H14" t="n">
-        <v>1955</v>
+        <v>49</v>
       </c>
       <c r="I14" t="n">
-        <v>6950.51</v>
+        <v>5656.25</v>
       </c>
       <c r="J14" t="n">
-        <v>10900</v>
+        <v>10310</v>
       </c>
       <c r="K14" t="n">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -9961,30 +11355,33 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>BOS, WENCOR</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); уже покупали у нас — репер; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; наценка высокая; цена с портала</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>10900</v>
+        <v>10310</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -9993,46 +11390,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7577741</t>
+          <t>RAA2196-4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FILTER</t>
+          <t>SWITCH</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>224</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>23.125</v>
+        <v>20300</v>
       </c>
       <c r="H15" t="n">
-        <v>49</v>
+        <v>28000</v>
       </c>
       <c r="I15" t="n">
-        <v>5656.25</v>
+        <v>121800</v>
       </c>
       <c r="J15" t="n">
-        <v>10310</v>
+        <v>164800</v>
       </c>
       <c r="K15" t="n">
-        <v>104</v>
+        <v>37.9</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>PROPONENT/WENCOR</t>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -10051,11 +11448,14 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); крупная сумма; заказа не было — зона роста; наценка уже ниже</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>10310</v>
+        <v>164800</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -10064,12 +11464,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RAA2196-4</t>
+          <t>CR3524-6-03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SWITCH</t>
+          <t>RIVET</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -10079,31 +11479,31 @@
         <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>1360</v>
       </c>
       <c r="G16" t="n">
-        <v>20300</v>
+        <v>65</v>
       </c>
       <c r="H16" t="n">
-        <v>28000</v>
+        <v>114</v>
       </c>
       <c r="I16" t="n">
-        <v>121800</v>
+        <v>88820</v>
       </c>
       <c r="J16" t="n">
-        <v>164800</v>
+        <v>136300</v>
       </c>
       <c r="K16" t="n">
-        <v>37.9</v>
+        <v>69</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>DISTRIBUTOR</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>BOS, MARKET</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -10122,11 +11522,14 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); крупная сумма; заказа не было — зона роста; наценка уже ниже</t>
+          <t>повторяющийся спрос (≥3 RFQ); крупная сумма; большой объём шт; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>164800</v>
+        <v>136300</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -10135,46 +11538,46 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CR3524-6-03</t>
+          <t>3036376</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>FILTER ELEMENT</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>1360</v>
+        <v>48</v>
       </c>
       <c r="G17" t="n">
-        <v>65</v>
+        <v>1710</v>
       </c>
       <c r="H17" t="n">
-        <v>114</v>
+        <v>2400</v>
       </c>
       <c r="I17" t="n">
-        <v>88820</v>
+        <v>75700</v>
       </c>
       <c r="J17" t="n">
-        <v>136300</v>
+        <v>111040</v>
       </c>
       <c r="K17" t="n">
-        <v>69</v>
+        <v>53.2</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>BOS, MARKET</t>
+          <t>AVIALL, SATAIR</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -10193,11 +11596,14 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); крупная сумма; большой объём шт; заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); варианты: 7 строк / 3 RFQ; крупная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>136300</v>
+        <v>147740</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -10206,46 +11612,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3036376</t>
+          <t>1C7003-3ABE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FILTER ELEMENT</t>
+          <t>CUSHION</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>3</v>
       </c>
       <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
         <v>7</v>
       </c>
-      <c r="F18" t="n">
-        <v>48</v>
-      </c>
       <c r="G18" t="n">
-        <v>1710</v>
+        <v>8704</v>
       </c>
       <c r="H18" t="n">
-        <v>2400</v>
+        <v>12400</v>
       </c>
       <c r="I18" t="n">
-        <v>75700</v>
+        <v>63124</v>
       </c>
       <c r="J18" t="n">
-        <v>111040</v>
+        <v>89900</v>
       </c>
       <c r="K18" t="n">
-        <v>53.2</v>
+        <v>42.5</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>DISTRIBUTOR</t>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>AVIALL, SATAIR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -10264,11 +11670,14 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); варианты ответов: 7 строк / 3 RFQ; крупная сумма; заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>147740</v>
+        <v>89900</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -10277,12 +11686,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1C7003-3ABE</t>
+          <t>67839</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CUSHION</t>
+          <t>CARTRIDGE VALVE ASSY</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -10292,31 +11701,31 @@
         <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>8704</v>
+        <v>3058.78</v>
       </c>
       <c r="H19" t="n">
-        <v>12400</v>
+        <v>4800</v>
       </c>
       <c r="I19" t="n">
-        <v>63124</v>
+        <v>55070.24</v>
       </c>
       <c r="J19" t="n">
-        <v>89900</v>
+        <v>81610</v>
       </c>
       <c r="K19" t="n">
-        <v>42.5</v>
+        <v>56.9</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BOS_ONLY</t>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -10335,11 +11744,14 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>89900</v>
+        <v>81610</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -10348,12 +11760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>113A9309-1</t>
+          <t>310A2042-3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BUSHING-PIVOT BOLT</t>
+          <t>PIN</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -10363,22 +11775,22 @@
         <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>2810</v>
+        <v>5306.25</v>
       </c>
       <c r="H20" t="n">
-        <v>4280</v>
+        <v>7700</v>
       </c>
       <c r="I20" t="n">
-        <v>54420</v>
+        <v>49237.5</v>
       </c>
       <c r="J20" t="n">
-        <v>84160</v>
+        <v>68250</v>
       </c>
       <c r="K20" t="n">
-        <v>52.3</v>
+        <v>43.1</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -10387,7 +11799,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>BOS, WENCOR</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -10410,7 +11822,10 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>84160</v>
+        <v>68250</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -10419,12 +11834,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>67839</t>
+          <t>2100002-01-104</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CARTRIDGE VALVE ASSY</t>
+          <t>RESTRAINT ASSY</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -10434,22 +11849,22 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>3058.78</v>
+        <v>4579.5</v>
       </c>
       <c r="H21" t="n">
-        <v>4800</v>
+        <v>7005</v>
       </c>
       <c r="I21" t="n">
-        <v>55070.24</v>
+        <v>36636</v>
       </c>
       <c r="J21" t="n">
-        <v>81610</v>
+        <v>55220</v>
       </c>
       <c r="K21" t="n">
-        <v>56.9</v>
+        <v>53</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -10458,7 +11873,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -10477,11 +11892,14 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); BOS отсечён ≈$18,000; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>81610</v>
+        <v>73220</v>
+      </c>
+      <c r="T21" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="22">
@@ -10490,12 +11908,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2100002-01-104</t>
+          <t>141A6075-3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RESTRAINT ASSY</t>
+          <t>ARM ASSY</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -10505,31 +11923,31 @@
         <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>4579.5</v>
+        <v>9537.5</v>
       </c>
       <c r="H22" t="n">
-        <v>7210</v>
+        <v>13800</v>
       </c>
       <c r="I22" t="n">
-        <v>49236</v>
+        <v>38637.5</v>
       </c>
       <c r="J22" t="n">
-        <v>73220</v>
+        <v>55000</v>
       </c>
       <c r="K22" t="n">
-        <v>48.5</v>
+        <v>41.8</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>PROPONENT/WENCOR</t>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>BOS, PROPONENT</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -10548,11 +11966,14 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>73220</v>
+        <v>55000</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -10561,12 +11982,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>310A2042-3</t>
+          <t>113A9309-1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PIN</t>
+          <t>BUSHING-PIVOT BOLT</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -10576,22 +11997,22 @@
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G23" t="n">
-        <v>5306.25</v>
+        <v>2670</v>
       </c>
       <c r="H23" t="n">
-        <v>7700</v>
+        <v>4130</v>
       </c>
       <c r="I23" t="n">
-        <v>49237.5</v>
+        <v>30920</v>
       </c>
       <c r="J23" t="n">
-        <v>68250</v>
+        <v>48360</v>
       </c>
       <c r="K23" t="n">
-        <v>43.1</v>
+        <v>54.8</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -10619,11 +12040,14 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); BOS отсечён ≈$35,800; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S23" t="n">
-        <v>68250</v>
+        <v>84160</v>
+      </c>
+      <c r="T23" t="n">
+        <v>35800</v>
       </c>
     </row>
     <row r="24">
@@ -10632,12 +12056,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>141A6075-3</t>
+          <t>310A2029-11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ARM ASSY</t>
+          <t>BOLT-SPECIAL</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -10647,22 +12071,22 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>9537.5</v>
+        <v>1822.1</v>
       </c>
       <c r="H24" t="n">
-        <v>13800</v>
+        <v>2300</v>
       </c>
       <c r="I24" t="n">
-        <v>38637.5</v>
+        <v>32496.8</v>
       </c>
       <c r="J24" t="n">
-        <v>55000</v>
+        <v>45710</v>
       </c>
       <c r="K24" t="n">
-        <v>41.8</v>
+        <v>52.4</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -10694,7 +12118,10 @@
         </is>
       </c>
       <c r="S24" t="n">
-        <v>55000</v>
+        <v>45710</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -10703,12 +12130,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>310A2029-11</t>
+          <t>1024366-311BHV</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BOLT-SPECIAL</t>
+          <t>BUMPER-ENDBAY</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -10718,31 +12145,31 @@
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G25" t="n">
-        <v>1822.1</v>
+        <v>270</v>
       </c>
       <c r="H25" t="n">
-        <v>2300</v>
+        <v>480</v>
       </c>
       <c r="I25" t="n">
-        <v>32496.8</v>
+        <v>33300</v>
       </c>
       <c r="J25" t="n">
-        <v>45710</v>
+        <v>45700</v>
       </c>
       <c r="K25" t="n">
-        <v>52.4</v>
+        <v>63.9</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BOS_ONLY</t>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BOS, SATAIR</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -10761,11 +12188,14 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S25" t="n">
-        <v>45710</v>
+        <v>45700</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -10774,12 +12204,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1024366-311BHV</t>
+          <t>815523-1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BUMPER-ENDBAY</t>
+          <t>PACKING</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -10789,31 +12219,31 @@
         <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="G26" t="n">
-        <v>270</v>
+        <v>1320</v>
       </c>
       <c r="H26" t="n">
-        <v>480</v>
+        <v>2010</v>
       </c>
       <c r="I26" t="n">
-        <v>33300</v>
+        <v>30135</v>
       </c>
       <c r="J26" t="n">
-        <v>45700</v>
+        <v>44810</v>
       </c>
       <c r="K26" t="n">
-        <v>63.9</v>
+        <v>52.3</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>DISTRIBUTOR</t>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>BOS, SATAIR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -10832,11 +12262,14 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S26" t="n">
-        <v>45700</v>
+        <v>44810</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -10845,12 +12278,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>815523-1</t>
+          <t>2100002-01-129</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PACKING</t>
+          <t>RESTRAINT SYSTEM - SYS</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -10860,31 +12293,31 @@
         <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>1320</v>
+        <v>5544.53</v>
       </c>
       <c r="H27" t="n">
-        <v>2010</v>
+        <v>8200</v>
       </c>
       <c r="I27" t="n">
-        <v>30135</v>
+        <v>22178.12</v>
       </c>
       <c r="J27" t="n">
-        <v>44810</v>
+        <v>33000</v>
       </c>
       <c r="K27" t="n">
-        <v>52.3</v>
+        <v>47.9</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>BOS_ONLY</t>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PROPONENT</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -10903,11 +12336,14 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S27" t="n">
-        <v>44810</v>
+        <v>33000</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -10916,12 +12352,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2100002-01-129</t>
+          <t>340-007-203-0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RESTRAINT SYSTEM - SYS</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -10934,28 +12370,28 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>5544.53</v>
+        <v>5686</v>
       </c>
       <c r="H28" t="n">
-        <v>8200</v>
+        <v>8400</v>
       </c>
       <c r="I28" t="n">
-        <v>22178.12</v>
+        <v>18738</v>
       </c>
       <c r="J28" t="n">
-        <v>33000</v>
+        <v>27960</v>
       </c>
       <c r="K28" t="n">
-        <v>47.9</v>
+        <v>51.2</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>PROPONENT/WENCOR</t>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>BOS, ENGINE</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -10974,11 +12410,14 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S28" t="n">
-        <v>33000</v>
+        <v>27960</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -10987,12 +12426,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>340-007-203-0</t>
+          <t>332A2930-90</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>BRACKET ASSY</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -11002,31 +12441,31 @@
         <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>5686</v>
+        <v>5500</v>
       </c>
       <c r="H29" t="n">
-        <v>8400</v>
+        <v>8100</v>
       </c>
       <c r="I29" t="n">
-        <v>18738</v>
+        <v>18100</v>
       </c>
       <c r="J29" t="n">
-        <v>27960</v>
+        <v>26100</v>
       </c>
       <c r="K29" t="n">
-        <v>51.2</v>
+        <v>43.1</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>DISTRIBUTOR</t>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>BOS, ENGINE</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -11045,11 +12484,14 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S29" t="n">
-        <v>27960</v>
+        <v>26100</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -11058,12 +12500,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>332A2930-90</t>
+          <t>65-0028-11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BRACKET ASSY</t>
+          <t>LIGHT</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -11073,31 +12515,31 @@
         <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G30" t="n">
-        <v>5500</v>
+        <v>2890</v>
       </c>
       <c r="H30" t="n">
-        <v>8100</v>
+        <v>4550</v>
       </c>
       <c r="I30" t="n">
-        <v>18100</v>
+        <v>17340</v>
       </c>
       <c r="J30" t="n">
-        <v>26100</v>
+        <v>25800</v>
       </c>
       <c r="K30" t="n">
-        <v>43.1</v>
+        <v>57.4</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>BOS_ONLY</t>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -11116,11 +12558,14 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S30" t="n">
-        <v>26100</v>
+        <v>25800</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -11129,46 +12574,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>65-0028-11</t>
+          <t>778000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LIGHT</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="G31" t="n">
-        <v>2890</v>
+        <v>189.95</v>
       </c>
       <c r="H31" t="n">
-        <v>4550</v>
+        <v>320</v>
       </c>
       <c r="I31" t="n">
-        <v>17340</v>
+        <v>12087.45</v>
       </c>
       <c r="J31" t="n">
-        <v>25800</v>
+        <v>20670</v>
       </c>
       <c r="K31" t="n">
-        <v>57.4</v>
+        <v>68.8</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>DISTRIBUTOR</t>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>PROPONENT, WENCOR</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -11187,11 +12632,14 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заметная сумма; заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); варианты: 4 строк / 3 RFQ; заметная сумма; заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S31" t="n">
-        <v>25800</v>
+        <v>21410</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -11200,46 +12648,46 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>778000</t>
+          <t>5011211</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FILTER</t>
+          <t>PIN INDICATOR</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="G32" t="n">
-        <v>189.95</v>
+        <v>490</v>
       </c>
       <c r="H32" t="n">
-        <v>320</v>
+        <v>800</v>
       </c>
       <c r="I32" t="n">
-        <v>12087.45</v>
+        <v>12740</v>
       </c>
       <c r="J32" t="n">
-        <v>20670</v>
+        <v>19920</v>
       </c>
       <c r="K32" t="n">
-        <v>68.8</v>
+        <v>63.3</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>PROPONENT/WENCOR</t>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>PROPONENT, WENCOR</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -11258,11 +12706,14 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); варианты ответов: 4 строк / 3 RFQ; заметная сумма; заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S32" t="n">
-        <v>21410</v>
+        <v>19920</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -11271,12 +12722,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5011211</t>
+          <t>0A296-0216HS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PIN INDICATOR</t>
+          <t>COVER-SEAT</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -11286,22 +12737,22 @@
         <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="G33" t="n">
-        <v>490</v>
+        <v>1040</v>
       </c>
       <c r="H33" t="n">
-        <v>800</v>
+        <v>1750</v>
       </c>
       <c r="I33" t="n">
-        <v>12740</v>
+        <v>11430</v>
       </c>
       <c r="J33" t="n">
-        <v>19920</v>
+        <v>19180</v>
       </c>
       <c r="K33" t="n">
-        <v>63.3</v>
+        <v>68.3</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -11333,7 +12784,10 @@
         </is>
       </c>
       <c r="S33" t="n">
-        <v>19920</v>
+        <v>19180</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -11342,12 +12796,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0A296-0216HS</t>
+          <t>649-411-981-0</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>COVER-SEAT</t>
+          <t>CLAMP</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -11357,22 +12811,22 @@
         <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G34" t="n">
-        <v>1040</v>
+        <v>422</v>
       </c>
       <c r="H34" t="n">
-        <v>1750</v>
+        <v>690</v>
       </c>
       <c r="I34" t="n">
-        <v>11430</v>
+        <v>13068</v>
       </c>
       <c r="J34" t="n">
-        <v>19180</v>
+        <v>18900</v>
       </c>
       <c r="K34" t="n">
-        <v>68.3</v>
+        <v>63.5</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -11381,7 +12835,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>BOS, ENGINE</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -11404,7 +12858,10 @@
         </is>
       </c>
       <c r="S34" t="n">
-        <v>19180</v>
+        <v>18900</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -11413,12 +12870,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>649-411-981-0</t>
+          <t>AS1633A10H0160</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLAMP</t>
+          <t>HOSE ASSY</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -11428,31 +12885,31 @@
         <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G35" t="n">
-        <v>422</v>
+        <v>870</v>
       </c>
       <c r="H35" t="n">
-        <v>690</v>
+        <v>1420</v>
       </c>
       <c r="I35" t="n">
-        <v>13068</v>
+        <v>11404</v>
       </c>
       <c r="J35" t="n">
-        <v>18900</v>
+        <v>17560</v>
       </c>
       <c r="K35" t="n">
-        <v>63.5</v>
+        <v>63.2</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>DISTRIBUTOR</t>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>BOS, ENGINE</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -11471,11 +12928,14 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S35" t="n">
-        <v>18900</v>
+        <v>17560</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -11484,12 +12944,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AS1633A10H0160</t>
+          <t>411N1527-1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HOSE ASSY</t>
+          <t>PAD</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -11499,22 +12959,22 @@
         <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>14</v>
+        <v>344</v>
       </c>
       <c r="G36" t="n">
-        <v>870</v>
+        <v>94.25</v>
       </c>
       <c r="H36" t="n">
-        <v>1420</v>
+        <v>164</v>
       </c>
       <c r="I36" t="n">
-        <v>11404</v>
+        <v>10283</v>
       </c>
       <c r="J36" t="n">
-        <v>17560</v>
+        <v>17448</v>
       </c>
       <c r="K36" t="n">
-        <v>63.2</v>
+        <v>73.5</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -11542,11 +13002,14 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; наценка высокая; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S36" t="n">
-        <v>17560</v>
+        <v>17448</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -11555,12 +13018,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>411N1527-1</t>
+          <t>65-49571-22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PAD</t>
+          <t>GASKET</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -11570,22 +13033,22 @@
         <v>3</v>
       </c>
       <c r="F37" t="n">
-        <v>344</v>
+        <v>149</v>
       </c>
       <c r="G37" t="n">
-        <v>94.25</v>
+        <v>121</v>
       </c>
       <c r="H37" t="n">
-        <v>164</v>
+        <v>210</v>
       </c>
       <c r="I37" t="n">
-        <v>10283</v>
+        <v>10212.52</v>
       </c>
       <c r="J37" t="n">
-        <v>17448</v>
+        <v>17200</v>
       </c>
       <c r="K37" t="n">
-        <v>73.5</v>
+        <v>69.7</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -11613,11 +13076,14 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; наценка высокая; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S37" t="n">
-        <v>17448</v>
+        <v>17200</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -11626,12 +13092,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>65-49571-22</t>
+          <t>38222-3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GASKET</t>
+          <t>CAP ASSY</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -11641,31 +13107,31 @@
         <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>149</v>
+        <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>121</v>
+        <v>2640</v>
       </c>
       <c r="H38" t="n">
-        <v>210</v>
+        <v>4160</v>
       </c>
       <c r="I38" t="n">
-        <v>10212.52</v>
+        <v>10560</v>
       </c>
       <c r="J38" t="n">
-        <v>17200</v>
+        <v>16640</v>
       </c>
       <c r="K38" t="n">
-        <v>69.7</v>
+        <v>57.6</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>BOS_ONLY</t>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>AVIALL</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -11684,11 +13150,14 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S38" t="n">
-        <v>17200</v>
+        <v>16640</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -11697,12 +13166,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>38222-3</t>
+          <t>65-54993-21</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CAP ASSY</t>
+          <t>PLATE</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -11712,31 +13181,31 @@
         <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
-        <v>2640</v>
+        <v>4005.75</v>
       </c>
       <c r="H39" t="n">
-        <v>4160</v>
+        <v>6100</v>
       </c>
       <c r="I39" t="n">
-        <v>10560</v>
+        <v>10155.75</v>
       </c>
       <c r="J39" t="n">
-        <v>16640</v>
+        <v>15470</v>
       </c>
       <c r="K39" t="n">
-        <v>57.6</v>
+        <v>52.3</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>DISTRIBUTOR</t>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>AVIALL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -11755,11 +13224,14 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S39" t="n">
-        <v>16640</v>
+        <v>15470</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -11768,12 +13240,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>65-54993-21</t>
+          <t>65-90305-86</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PLATE</t>
+          <t>FILTER MAINTENANCE KIT</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -11783,22 +13255,22 @@
         <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G40" t="n">
-        <v>4005.75</v>
+        <v>573.49</v>
       </c>
       <c r="H40" t="n">
-        <v>6100</v>
+        <v>980</v>
       </c>
       <c r="I40" t="n">
-        <v>10155.75</v>
+        <v>9127.450000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>15470</v>
+        <v>15150</v>
       </c>
       <c r="K40" t="n">
-        <v>52.3</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -11830,7 +13302,10 @@
         </is>
       </c>
       <c r="S40" t="n">
-        <v>15470</v>
+        <v>15150</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -11839,12 +13314,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>65-90305-86</t>
+          <t>NAS1756-36</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FILTER MAINTENANCE KIT</t>
+          <t>STREAMER - WARNING</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -11854,31 +13329,31 @@
         <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G41" t="n">
-        <v>573.49</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>980</v>
+        <v>18</v>
       </c>
       <c r="I41" t="n">
-        <v>9127.450000000001</v>
+        <v>7559.2</v>
       </c>
       <c r="J41" t="n">
-        <v>15150</v>
+        <v>14684</v>
       </c>
       <c r="K41" t="n">
-        <v>64.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>BOS_ONLY</t>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PROPONENT, WENCOR</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -11897,11 +13372,14 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; наценка высокая; цена с портала</t>
         </is>
       </c>
       <c r="S41" t="n">
-        <v>15150</v>
+        <v>14684</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -11910,12 +13388,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NAS1756-36</t>
+          <t>649-411-983-0</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>STREAMER - WARNING</t>
+          <t>CLAMP</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -11925,54 +13403,57 @@
         <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G42" t="n">
-        <v>8.710000000000001</v>
+        <v>429</v>
       </c>
       <c r="H42" t="n">
-        <v>18</v>
+        <v>640</v>
       </c>
       <c r="I42" t="n">
-        <v>7559.2</v>
+        <v>9180</v>
       </c>
       <c r="J42" t="n">
-        <v>14684</v>
+        <v>14220</v>
       </c>
       <c r="K42" t="n">
-        <v>96.40000000000001</v>
+        <v>58.5</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>PROPONENT/WENCOR</t>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>PROPONENT, WENCOR</t>
+          <t>BOS, ENGINE</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); уже покупали у нас — репер</t>
         </is>
       </c>
       <c r="S42" t="n">
-        <v>14684</v>
+        <v>14220</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -11981,12 +13462,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>649-411-983-0</t>
+          <t>2D8007-1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CLAMP</t>
+          <t>STRAP</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -11996,22 +13477,22 @@
         <v>3</v>
       </c>
       <c r="F43" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="G43" t="n">
-        <v>429</v>
+        <v>180</v>
       </c>
       <c r="H43" t="n">
-        <v>640</v>
+        <v>270</v>
       </c>
       <c r="I43" t="n">
-        <v>9180</v>
+        <v>9220</v>
       </c>
       <c r="J43" t="n">
-        <v>14220</v>
+        <v>14210</v>
       </c>
       <c r="K43" t="n">
-        <v>58.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -12020,30 +13501,33 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>BOS, ENGINE</t>
+          <t>AVIALL, BOS, SATAIR</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1080</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); уже покупали у нас — репер</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S43" t="n">
-        <v>14220</v>
+        <v>14210</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -12052,12 +13536,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2D8007-1</t>
+          <t>210N0013-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>STRAP</t>
+          <t>INSULATION</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -12067,31 +13551,31 @@
         <v>3</v>
       </c>
       <c r="F44" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>180</v>
+        <v>3300</v>
       </c>
       <c r="H44" t="n">
-        <v>270</v>
+        <v>5030</v>
       </c>
       <c r="I44" t="n">
-        <v>9220</v>
+        <v>9200</v>
       </c>
       <c r="J44" t="n">
-        <v>14210</v>
+        <v>14020</v>
       </c>
       <c r="K44" t="n">
-        <v>65.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>DISTRIBUTOR</t>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>AVIALL, BOS, SATAIR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -12110,11 +13594,14 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S44" t="n">
-        <v>14210</v>
+        <v>14020</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -12123,12 +13610,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>210N0013-10</t>
+          <t>RC3506-1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>INSULATION</t>
+          <t>BRACKET</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -12138,31 +13625,31 @@
         <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G45" t="n">
-        <v>3300</v>
+        <v>840</v>
       </c>
       <c r="H45" t="n">
-        <v>5030</v>
+        <v>1370</v>
       </c>
       <c r="I45" t="n">
-        <v>9200</v>
+        <v>8420</v>
       </c>
       <c r="J45" t="n">
-        <v>14020</v>
+        <v>13050</v>
       </c>
       <c r="K45" t="n">
-        <v>52.4</v>
+        <v>63.1</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>BOS_ONLY</t>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BOS, SATAIR</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -12181,11 +13668,14 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста</t>
         </is>
       </c>
       <c r="S45" t="n">
-        <v>14020</v>
+        <v>13050</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -12194,12 +13684,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RC3506-1</t>
+          <t>71889-3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BRACKET</t>
+          <t>RING, UPPER</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -12209,31 +13699,31 @@
         <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G46" t="n">
-        <v>840</v>
+        <v>816.86</v>
       </c>
       <c r="H46" t="n">
-        <v>1370</v>
+        <v>1380</v>
       </c>
       <c r="I46" t="n">
-        <v>8420</v>
+        <v>7351.74</v>
       </c>
       <c r="J46" t="n">
-        <v>13050</v>
+        <v>12420</v>
       </c>
       <c r="K46" t="n">
-        <v>63.1</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>DISTRIBUTOR</t>
+          <t>PROPONENT/WENCOR</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>BOS, SATAIR</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -12252,11 +13742,14 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; цена с портала</t>
         </is>
       </c>
       <c r="S46" t="n">
-        <v>13050</v>
+        <v>12420</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -12265,12 +13758,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>71889-3</t>
+          <t>310A2043-2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RING, UPPER</t>
+          <t>CAP</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -12283,28 +13776,28 @@
         <v>9</v>
       </c>
       <c r="G47" t="n">
-        <v>816.86</v>
+        <v>837.2</v>
       </c>
       <c r="H47" t="n">
-        <v>1380</v>
+        <v>1370</v>
       </c>
       <c r="I47" t="n">
-        <v>7351.74</v>
+        <v>7551.6</v>
       </c>
       <c r="J47" t="n">
-        <v>12420</v>
+        <v>12330</v>
       </c>
       <c r="K47" t="n">
-        <v>68.90000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>PROPONENT/WENCOR</t>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -12323,11 +13816,14 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S47" t="n">
-        <v>12420</v>
+        <v>12330</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -12336,12 +13832,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>310A2043-2</t>
+          <t>140N2147-2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CAP</t>
+          <t>RING</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -12351,22 +13847,22 @@
         <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G48" t="n">
-        <v>837.2</v>
+        <v>2604</v>
       </c>
       <c r="H48" t="n">
-        <v>1370</v>
+        <v>3970</v>
       </c>
       <c r="I48" t="n">
-        <v>7551.6</v>
+        <v>7641.5</v>
       </c>
       <c r="J48" t="n">
-        <v>12330</v>
+        <v>11640</v>
       </c>
       <c r="K48" t="n">
-        <v>63.2</v>
+        <v>52.3</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -12398,7 +13894,10 @@
         </is>
       </c>
       <c r="S48" t="n">
-        <v>12330</v>
+        <v>11640</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -12407,12 +13906,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>140N2147-2</t>
+          <t>CR3524-6-04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>RING</t>
+          <t>RIVET</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -12422,22 +13921,22 @@
         <v>3</v>
       </c>
       <c r="F49" t="n">
-        <v>10</v>
+        <v>135</v>
       </c>
       <c r="G49" t="n">
-        <v>2604</v>
+        <v>43</v>
       </c>
       <c r="H49" t="n">
-        <v>3970</v>
+        <v>74</v>
       </c>
       <c r="I49" t="n">
-        <v>7641.5</v>
+        <v>5999.5</v>
       </c>
       <c r="J49" t="n">
-        <v>11640</v>
+        <v>10405</v>
       </c>
       <c r="K49" t="n">
-        <v>52.3</v>
+        <v>73.8</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -12465,11 +13964,14 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; наценка высокая; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S49" t="n">
-        <v>11640</v>
+        <v>10405</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -12478,12 +13980,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>60477</t>
+          <t>BACN10JR3CFD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BUSHING</t>
+          <t>NUTPLATE</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -12493,22 +13995,22 @@
         <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>6</v>
+        <v>3122</v>
       </c>
       <c r="G50" t="n">
-        <v>1010</v>
+        <v>2.3</v>
       </c>
       <c r="H50" t="n">
-        <v>1750</v>
+        <v>4.3</v>
       </c>
       <c r="I50" t="n">
-        <v>6747.6</v>
+        <v>7280</v>
       </c>
       <c r="J50" t="n">
-        <v>10920</v>
+        <v>10380</v>
       </c>
       <c r="K50" t="n">
-        <v>63.7</v>
+        <v>87</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -12517,7 +14019,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>BOS, PROPONENT</t>
+          <t>WENCOR</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -12536,11 +14038,14 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
         </is>
       </c>
       <c r="S50" t="n">
-        <v>10920</v>
+        <v>10380</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -12549,12 +14054,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CR3524-6-04</t>
+          <t>A35789-2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>RIVET</t>
+          <t>SPRING</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -12564,31 +14069,31 @@
         <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="G51" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H51" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I51" t="n">
-        <v>5999.5</v>
+        <v>5775</v>
       </c>
       <c r="J51" t="n">
-        <v>10405</v>
+        <v>10200</v>
       </c>
       <c r="K51" t="n">
-        <v>73.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>BOS_ONLY</t>
+          <t>DISTRIBUTOR</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>AVIALL, BOS</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -12607,11 +14112,14 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; наценка высокая; только BOS — осторожно</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; наценка высокая</t>
         </is>
       </c>
       <c r="S51" t="n">
-        <v>10405</v>
+        <v>10200</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -12620,12 +14128,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BACN10JR3CFD</t>
+          <t>332A2350-11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NUTPLATE</t>
+          <t>TUBE ASSY</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -12635,31 +14143,31 @@
         <v>3</v>
       </c>
       <c r="F52" t="n">
-        <v>3122</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
-        <v>2.3</v>
+        <v>2200</v>
       </c>
       <c r="H52" t="n">
-        <v>4.3</v>
+        <v>3350</v>
       </c>
       <c r="I52" t="n">
-        <v>7280</v>
+        <v>6600</v>
       </c>
       <c r="J52" t="n">
-        <v>10380</v>
+        <v>10060</v>
       </c>
       <c r="K52" t="n">
-        <v>87</v>
+        <v>52.4</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>PROPONENT/WENCOR</t>
+          <t>BOS_ONLY</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>WENCOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -12678,157 +14186,18 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>повторяющийся спрос (≥3 RFQ); большой объём шт; заказа не было — зона роста; наценка высокая; цена с портала</t>
+          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; только BOS — осторожно</t>
         </is>
       </c>
       <c r="S52" t="n">
-        <v>10380</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>A35789-2</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>SPRING</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>3</v>
-      </c>
-      <c r="E53" t="n">
-        <v>3</v>
-      </c>
-      <c r="F53" t="n">
-        <v>105</v>
-      </c>
-      <c r="G53" t="n">
-        <v>36</v>
-      </c>
-      <c r="H53" t="n">
-        <v>70</v>
-      </c>
-      <c r="I53" t="n">
-        <v>5775</v>
-      </c>
-      <c r="J53" t="n">
-        <v>10200</v>
-      </c>
-      <c r="K53" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>DISTRIBUTOR</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>AVIALL, BOS</t>
-        </is>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; наценка высокая</t>
-        </is>
-      </c>
-      <c r="S53" t="n">
-        <v>10200</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>332A2350-11</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>TUBE ASSY</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>3</v>
-      </c>
-      <c r="E54" t="n">
-        <v>3</v>
-      </c>
-      <c r="F54" t="n">
-        <v>3</v>
-      </c>
-      <c r="G54" t="n">
-        <v>2200</v>
-      </c>
-      <c r="H54" t="n">
-        <v>3350</v>
-      </c>
-      <c r="I54" t="n">
-        <v>6600</v>
-      </c>
-      <c r="J54" t="n">
         <v>10060</v>
       </c>
-      <c r="K54" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>BOS_ONLY</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>повторяющийся спрос (≥3 RFQ); заказа не было — зона роста; только BOS — осторожно</t>
-        </is>
-      </c>
-      <c r="S54" t="n">
-        <v>10060</v>
+      <c r="T52" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S54"/>
+  <autoFilter ref="A1:T52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>